--- a/dynamic-crawling/yanolja_data.xlsx
+++ b/dynamic-crawling/yanolja_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D384"/>
+  <dimension ref="A1:D502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>친구들 3명에서 급하게 예약을 했던 숙손데 와.. 우선 프론트 직원님들.. 진짜 너무 친절해서 기분이 좋았습니다. 2박3일 일정이였는데 기분좋게 하루를 시작했고 숙소 위치도 그냥 완전 좋아요..!!!!! 애월은 마스터했습니다. ㅋㅋㅋㅋ 위치 금액 시설이용 서비스 위생 뭐 하나 빠지는거없이  (친구들도인정) 너무 편하게 잘 쉬다가 갑니다 ㅎㅎㅎ 후기 잘 안쓰는데 여기는 꼭 쓰고싶어서 이렇게 남깁니다!오늘도 좋은 하루 되세용:)🍀</t>
+          <t>유명한 제천 리솜 포레스트! 가족여행으로 다녀왔어요! 가족여행으로 인기 많은 이유를 알겠더라고요. 편의시설을 이용하기 편한 레스트리에 묵었는데 방도 넓고 쾌적하고 힐링하기 딱 좋았습니다. 이날 워크샵 온 회사들이 있었는데도 참 조용하고 즐기기 좋았어요 야외 스파도 종류가 다양해서 가족여행으로 제격인 것 같았습니다. 실내 수영장도 넓고 아동들을 위한 수영장도 잘 되어있구요! 유수풀은 성인이 즐겨도 참 재미있습니다😆💕 야외 스톤스파는 주말엔 예약을 해야한다는데 평일엔 자유롭게 이용가능했어요! 포레스트는 독채감성이 낭낭하고 레스트리는 비교적 최신식이라 하더라고요! S30 추천합니다 👍🏻👍🏻🌿꿀팁 체크인은 15시지만 12시부터 방배정을 합니다. 일찍와서 배정받은 후 스파를 즐기세요! 🌿중간쯤에 있는 스톤스파에서 사진이 젤 잘나와요</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>욕실 및 객실 다 깨끗하고 시설이 좋았으며 바다뷰가 너무 좋았고 여름에 다시 올 생각임^^</t>
+          <t>고객 응대하는 프론트 직원들 훌륭하셨습니다다만 조식 관련 응대 직원 교육은 좀 더 필요해 보입니다최근 지은 건물이라 대체로 깨끗했으나 벽이나 조명이 먼지가 가득했습니다머문 호실 화장실문에서 삐끄덕 소리가 났습니다수영장 좋았고 조식을 포함해 입주해 있는 음식점 평범했습니다 가격이 있는 편입니다규모와 호실 수에 비해 주차장이 빠듯합니다위치상 차가 필요한 곳인데 주차시설이 더 넓지 않은건 아쉅습니다</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -480,7 +480,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>저는 어딜가든 진짜 리뷰 안쓰는데..처음간 여행에 너무좋은기억이라서 글몇자 올려봅니다. 미리예약하고 가서 걱정없이 갔는데 너무감사하게 호텔사장님께서 친히전화주셔서. 오션뷰 테라스있는곳으로 업그레이드 해주셔서 너무 편히 쉬게되었어요 여행은 잠을잘자야 편하다고 하든데. 따뜻하게 자고 왔어요 시설도 깨끗하고.,  2박했는데 청소도해주시고. 지하에 세탁기.건조기도 있어서. 옷을 많이 안챙겨가도 좋을거같아요 로비에 카페가 있어서 커피도 먹을수있고. 암튼 너무~너무 좋았어요  바닷가앞이라 나가서 산책을해도 좋고 주위에 밥집들이 유명한곳이 다 근처에 있어서 더더욱 좋았어요 .강추합니다👍👍👍👍👍</t>
+          <t>숙소가 자연속에 있어서 힐링되는 느낌이 좋아요. 객실 안도 깔끔하고 산과 어울리는 객실 분위기가 마음에 들었습니다. 직원분들도 다 친절하시고 전체적인 호텔 분위기가 좋네요. 부대시설도 이것저것 많아서 남녀노소 누가 가도 재밌게 즐기고 올 수 있을 것 같아요. 스파도 마음에 들었어요. 다만 저는 평일에 갔는데도 사람이 좀 있었다고 느껴졌는데 주말에 가면 완전 미어 터질 것 같다는 생각이 드네요 ㅠㅠ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -488,11 +488,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>제주도 당일예약해서  하루묵게 되엇어요~편의점도 바로앞에잇고 간단히맥주한캔 마시고 잘 쉬다갑니다~ 앞에 뷰가 참이뻣는데 날씨가 흐리고 바람많이 불어서  사진을 못찍엇어요ㅜㅜ화장실휴지도  접어놓으신센스 ㅋ 깔끔햇어요직원분도 친절하셧어요 춥지않게 푹 잣네요다음에 또신랑이 오자구햇어요^^</t>
+          <t>포레스트 52동 01호 숙박했네요.장점은 프라이빗. 조용히 숙박하시면레스트리보다는 포레스트가 좋네요.거실크기, 주방시설, 밥먹고 운동(포레스트는 거리가있으니 카트 아니면 운동)등은 확실히 포레스트가 낫네요. 부부의세계나. 시크릿가든 촬영지도 있으니 찾아보는것도  소소 재미구요.주변시설  자주 이용하실거면 레스트리 이용하시는걸추천 드립니다.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>오션뷰 참 좋았어요~설 연휴 길어 잠깐 다녀왔는데 눈 비 바람에 엄청난 파도...뷰 좋은 테라스 이용 못 해 아쉬움은남아머요깨끗하고 따뜻하고 둘이 휴식하기 좋은숙소 다음에 또 이용 할꺼예요^^</t>
+          <t>3월에 마침 눈까지와서 경치가 정말 끝내줬습니다. 시설들도 너무 깨끗하고 최고에요! 다음에 또 방문할 예정입니다!!</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -516,7 +516,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>곽지 해수욕장에서 해수욕하고 놀기 넘 좋아요~ 뷰도 끝내주고 숙소 올라오는 계단 위에 샤워기로 모래도 씻을 수 있고 방도 작지 않고 침구도 깨끗하구요!! 침대 두개 붙여서 아이가 떼굴떼굴 굴러다니며 잤네요^^ 그리고 물놀이용품 없어도 구명조끼, 튜브, 돗자리, 모래놀이 등 다 빌려사용할 수 있어서 넘 좋았어요~~담에 꼭 또 가려구요^^ 잘 지내다 갑니다^^</t>
+          <t>전부터 가고 싶었던 리솜 레스트리 방문!! 로비부터 전체적 직원분들이 친절합니다.방도 깨끗하고 넓으며사진 외 더블 침대방 하나 더 있어요해브나인 스파도 춥다 느낄 수 있지만구석구석 잘 찾아보면 따뜻한 곳도 있어요취사가 안되서 음식을 리솜 포레스트나 레스트리 식당을 이용해야하는 부분이 아쉽지만 전체적으로 만족스럽고 재방문의사 있습니다</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -528,7 +528,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7년전에 왔을때랑 별반 다르지 않아서 깜짝 놀랐어요!바닷가 앞이라 숙박객들도 대부분 바다에서 놀다가 오실분들이 많으실것같은데 복도며 객실이며 깔끔해서 좋았어요.아기랑 간다고 말씀드렸더니 침대도 붙여주시고덕분에 아기 떨어질 걱정없이 셋이서 편하게 잤어요ㅎㅎ바다에서 재밌게 놀고 숙소가 가까우니 너무 좋아요!7년전 여행때도 좋았는데이번에도 즐겁게 하루 지내다 가요!고맙습니다~</t>
+          <t>추석때 가족과 조카와 함께 2박 투숙했는데 가족들은 강릉 라카이가 더 좋았다고 하네요^^;; s70객실 7명대가족 투숙하기 넓고 좋았어요. 다만 거실이 들어갔을때 좀 답답 해서 그랬나봐요. 직원들은 모두 친절했어요!! 최고! 산책하기도 좋았어요.추가로 청풍케이블카 최고!! 강추!! 근처 황금떡갈비 꼭 드세요!!</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -536,11 +536,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>숙소 경치 너무 너무 이뻐요 사진이랑 똑같아요 사장님분들도 전부 친절 하시고 주차공간도 넉넉하게 지상 지하 둘다 있어서 너무 좋네요 물도 잘나오고 방도 깔끔해서 만족 했습니다 근처에도 먹거리 많고 마트랑 편의점 다이소등 다 가까워서 편해요 다음에도 재방문 할거 같아요</t>
+          <t>깨끗하고 친절하고 다 좋은데4인방 S20예약 했는데 2인 싱글베드방이 좁아 쇼파및 탁자 밀고 이부자리 깔아야돼요4인 이라기엔 이해아가 안돼요</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -548,11 +548,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>오션뷰도 좋고 침대 쿠션도 좃고 숙면을 축한 하룻밤이였네요..방크기가 조금작고 디저트가 안보여서 아쉬웠어요..아침에 일어나 모닝커피를 못마셨네요....곽지해수욕장이 바로 코앞이라  바다는 실컷봤습니다, .친구들이 넘넘 잘 잡았데요..다음에 또 찾고 싶네요.ㅎ</t>
+          <t>직원들도 친절하고 시설도 깨끗하고 좋았어요조식도 맛있었구요생각보다 빌라동은 하이엔드 느낌은 아니구요사실 숙소보다 리솜포레스트는 부지 자연 조경 등이 너무 아름다워서 있기만해도 힐링되더라구요성수기 스파가격이 비싸서 스파+숙박 가격일때 숙박이 십만원대였어서 적당히 그정도 맞았다 생각합니다</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>좀 연식이있는 복도가 당황스러웠지만내부와 뷰가 대만족이였습니다프론트 직원분들과 객실담당하시는분들도 모두모두 친절하셨어요한가지 아쉬운점은 수건이 좀 많이 낡았어요 수건이 교체되면 어떨까 싶었어요그리고 냉장고문고리가 부러져있던데 교체하시길 ㅋ마지막으로 객실에 커피나티가 없어서 아쉬웠습니다하지만 이가격에 이런뷰는 정말 대박이였고 잘쉬었다갑니다</t>
+          <t>넘좋았던곳 또또가고싶당 2박했는데  하루는 레스트리 하루는포레스트 해브나인스파ㆍ인피니트풀ㆍ몬도키친조식ㆍ마묵라운지카페등  다좋았고 평일이라 스톤스파사람도많이붐비지않아 대기별로없어 두번이용했고 조식도 체크아웃하고 늦은시간에가서 편하게잘먹고왔고 쌀국수맛있었음ㅋ 자연과힐링하는숲캉스하러 또가고싶당</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -576,7 +576,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>부대시설이 좋았어요~치약이랑 칫솔 .로션까지 구비되어 있어 넘좋았어요 아이들과 부모님 이 같이 가니 침대 배치도 넓게 쓸수있게 해주셔서 좋았고 ~객실서 음식도 먹을수 있다고하셔서 좋았어요~바로앞 바닷가라 산책하기도 좋아요.편의점도 바로앞에 있어요</t>
+          <t>부모님 칠순으로 여행을 다녀왔습니다산책로나 정관이 잘 꾸며져있어 부모님이 매우 좋아하셨어요부대시설도 다양하게 있어서 큰 불편함 없이 다양하게 즐길 수 있었어요객실내에 냉장고가 작은 게 흠이에요취사가 가능한 객실이 아니라 그런것 같긴해요그외엔 전반적으로 가족모두 만족한 편이였어요</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -588,7 +588,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>부대시설이 좋았어요~치약이랑 칫솔 .로션까지 구비되어 있어 넘좋았어요 아이들과 부모님 이 같이 가니 침대 배치도 넓게 쓸수있게 해주셔서 좋았고 ~객실서 음식도 먹을수 있다고하셔서 좋았어요~바로앞 바닷가라 산책하기도 좋아요.편의점도 바로앞에 있어요</t>
+          <t>부모님 칠순으로 여행을 다녀왔습니다산책로나 정관이 잘 꾸며져있어 부모님이 매우 좋아하셨어요부대시설도 다양하게 있어서 큰 불편함 없이 다양하게 즐길 수 있었어요객실내에 냉장고가 작은 게 흠이에요취사가 가능한 객실이 아니라 그런것 같긴해요그외엔 전반적으로 가족모두 만족한 편이였어요</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>프론트 여직원분 넘친절하시고 객실 수건.침실정리 등 잘해주셔서 3박동안 기분좋았습니다.튜브바람넣는거.탈수기.세탁실 다 있어서 넘편했어요~곽지로 온다면 무조건 마레보비치에 머물 예정입니다</t>
+          <t>성인2명에 19개월아기1명 S20객실에 머물렀는데요,룸컨디션도 좋고 따뜻하고 전망도좋았어요 아기와 함께라서 바닥이 온돌인게 좋네요ㅎㅎ 대부분의 부대시실은 포레스트클럽 건물에 있는데 야외를 통해 연결되어있는점이 좀 아쉬워요</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -608,11 +608,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>위치도 좋고 경치는 더 좋은데 도보로 식당 찾기는 좀 애매하더라구요 객실도 욕실도 깨끗하고 다 좋은데 침대 매트리스가 좀 많이 흔들리고 다음 날 허리가 좀 아프더라구요 뭔가 조금 아쉬웠어요</t>
+          <t>많은 사람들이 찾는곳인만큼너무너무 만족스러웠습니다ㅎ친절함이며 서비스, 객실상태 등부족한 부분 하나없이 너무만족하고 잘 쉬다왔습니다</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -624,7 +624,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>부모님 숙소잡아드렸는데 전망이 너무좋고해수욕장도 가깝고 방도 따뜻해서 좋으셨다고해요그리고 직원분들 너무 친절하다고 칭찬하셨습니다그리고 대부분 연박청소 안해주시던데청소도 해주셨데요 매우 흡족해하셨어요다음에 또 이용하여 싶으시대요 👍 👍 👍</t>
+          <t>예전부터 가보고 싶었곳이라 기대가 컸고 기대만큼 만족스러웠습니다. 카트 운영해주시는 직원분들도 너무 친절하시고 조경이 참 예뻐서 머무는 내내 힐링하는 기분이었습니다. 체크아웃 후에 사용한 수영장도 물이 깨끗하고 수온이 차갑지않게 딱좋아서 정말 잘 놀다왔네요. 다음엔 가을 단풍 들었을때 또 가보고싶어요.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>부모님 숙소잡아드렸는데 전망이 너무좋고해수욕장도 가깝고 방도 따뜻해서 좋으셨다고해요그리고 직원분들 너무 친절하다고 칭찬하셨습니다그리고 대부분 연박청소 안해주시던데청소도 해주셨데요 매우 흡족해하셨어요다음에 또 이용하여 싶으시대요 👍 👍 👍</t>
+          <t>최소 5인 이상 즐기기에 아주 좋은 숙소입니다. 레스트리는 포레스트보다 신축 건물이라 전반적으로 깨끗하고 좋네요. 침구류 푹신하고 편하고 세면대 수압도 세서 이용하기 좋았습니다. 주변이 전부 산이라 차가 없으면 이동이 힘들지만 숙소 내에서 대부분 해결할 수 있다는 장점도 있습니다.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>일단 공항에서 가까워 접근성이 좋고 제가 제일 중요하게 생각하는 침구와 청결상태가 아주 좋습니다. 창문밖으로 보이는 제주바다도 너무 좋아요</t>
+          <t>해브나인스파만 이용하다가 숙소와봤는데너무 깔끔하고 고급스럽네용 로비도 층고도 높고, 부대시설도 너무좋았어요^^침구도 너무편해서 진짜 잘 놀았어요~!또 오고싶은곳중 하나에요!!</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -660,7 +660,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>숙소 너무 깔끔했구 연박하면 수건이랑 물도 다시 받을 수 있어요!! 직원분들도 친절하세요! 화장대도 있어서 너무 좋았습니당</t>
+          <t>눈쌓은 마운틴뷰의 객실은 최고였습니다. 객실 내부도 청결했습니다. 다만 4인실인데 이불및베개를 추가로 주셨으나, 마땅히 깔 공간이 협소한점은 아쉬웠습니다. 해당 객실은 2인실로 제한하는게 쾌적한 환경에서 숙박이 가능할것으로 사료됩니다</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -672,7 +672,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>아주 좋아요바다가 앞에 있어서아침에 걷기가 딱입니다실내도 깨끗하고침구도 편안합니다주변에 맛집도많고  아주 잘 쉬다가 갑니다</t>
+          <t>조경이쁘고~이숙소만의 매력이 너무 잘 느껴지는 초록초록한 숙소였어요~~기대를 많이 안해서 그런지카트타야하는 불편함도 있고  청소가 미흡한부분도 있었겠지만~~ 그런거 감안해도 매력있고 편안하고 즐거운 시간이었어요~조식도 아이한명은 무료행사해서 가성비 좋게 잘 먹었고~ 스파도 낡았던 부분도 있지만 특색있고 아이들이 너무 좋아했어요~~</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -684,7 +684,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>직원분들이 매우 친절하셨습니다. 제주에서 여러군데 갔던 곳들 중에 제일 직원분들이 친절하셨습니다. 다음에 이쪽을 방문하게 된다 면 재방문 할 의사가 있어요.</t>
+          <t>산 속이라 공기도 좋고 산책도 하며 오랜만에  자연을 느낄수 있어 좋았고 겨울에 야외에서 온천을 보며 경치를 보는 즐거움이 컸어요  오락실편의점 음식점도 있어 크게 불편함 없이 잘 이용하고 왔어요</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -692,11 +692,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>아름다운 곽지해수욕장을 전망할 수 있습니다.묵는 사흘 내내 날씨가 좋지 않았지만 방이 따뜻해서 괜찮았습니다. 특히 침대가 탄탄하고 넓어 잠을 잘 잤습니다.  침대는 만점입니다.직원들도 친절합니다.</t>
+          <t>레스트리 타워가 전체적으로 다 깔끔하고 조용해서 좋았아요 s20 룸도 깨끗하고 두명이 지내기 좋은 크기였고 눈이 쌓여서 그런지 뷰도 너무 좋았습니다^^리솜 안에 모든 시설이 다 있어서 굳이 밖으로 나가지 않아도 돼서 편리했고 스파도 너무 좋았어요 마침 눈이 내려서 눈 맞으면서 하는 스파가 낭만 있었어요ㅎㅎ 그리고 단락 흑백 사진관도 이용했는데 사진도 잘 나오고 추억 남기기 너무 좋았습니다단점이나 아쉬웠던 부분은 딱히 없었습니다다만 저는 편리함을 추구하는 편이라 레스트리에서 묵었는데 포레스트동에 있었더라면 왔다갔다 하기 조금 불편했을 것 같아요 그래도 뷰는 포레스트가 훨씬 예쁩니다!ㅎㅎ직원분들도 다 친절하시고 1박2일은 부족하단 생각이 드네요ㅎㅎ 다음에는 좀 오래 있다가 가야겠어요^^리솜에서 너무 만족스럽게 지내다 갑니다!</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -708,7 +708,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>가성비 최고 숙소였어요!!!먼저 직원분들 너무나 친절하시고  웰컴 커피  맛있어서 물어보니 커피콩이 비싼거더라고요여기 커피맛집인듯!퇴실할때  먹은 라떼랑   직접 담그신 청귤청으로 만든 에이드도 진짜  맛있었어요4인가족 패밀리 스위트에 머물렀는데 레지던스호텔처럼 인덕션, 가스렌지, 싱크대 갖추어져 있었어요  냉장고도 나름 컸구요거실에 스타일러 있어서 외출 후 옷관리 했구요방에  트원 침대  2대 있어 4인가족이 넓게 이용하기 좋았어요  침대 편하고 침구류 포근하고 편해서 꿈잘잤어요  온돌로 바닥도 따뜻하고 공기도 따뜻해서 편히 잘 쉬었어요물론 청소상태도 좋았구요  주변에 카페,식당 가깝고 곽지 해수욕장 바로 앞이라 위치도 좋았어요  여름에 가면 물놀이 하기에도 좋겠더라고요2박 모두 머물렀는데 돌아올 때 더 있고 싶어서 많이 아쉬웠어요다음에도 또  방문 예정이랍니다</t>
+          <t>숲사이에 숙소가 있어서 공기가 너무 좋더라구요~다만 벌레가 있는건 감안해야 할 것 같아요보일러가 쎄서 건조하긴했는데(수영복 온돌방에 펼쳐두니 한시간만에 다마름 ㅋㅋ)잘 조절해서 이용하면 될 것 같아요스파도 이용했는데 평일이라 그런지 사람도 많이 없고 편하게 잘 이용했습니다!! 편의시설은 이용은 안했지만 오락실, 만화카페, vr 등 다양하게 있었고 편의점도 크고 치킨집이나 다른 음식점들도 다양하게 있어서 좋았어요저희는 밖에 픽업되는 식당이 있어서 나가서 먹었습니다~(술때매 차를 못끌고가서ㅠ)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -720,7 +720,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>와 정말 추천해요. 3박4일 제주 첫날 숙소였는데 침대가 일단 무지 푹신하고 편하고 깨끗해요. 걸어서 1분거리 해수욕장이라 그냥 수영복입고 바로 바다안에 들어가서 나와서 숙소에서 씻기도 편햇습니다. 뱅기타고 첫날 열심히 놀아서 피곤햇는데 담날 푹자고일어나서 컨디션좋았어요. 글고 카운터분들이 무지 친절해서 또한번놀랏어요. 사장님들인지 모르겠지만 서계신분들마다 친절하시고 커앤크도 맛있게 먹엇습니다. 24시 언제든 시킬수있다는 편리함.. 주차장도 지상.지하 넓어서 여유있어서 좋구요. 진짜 너무강추합니다. 시설.깨끗.친절. 너무너무 강추합니다.</t>
+          <t>말모말모~ 진짜 최고였습니다! 가격때문에 미루고 미뤘던 리솜 진짜 너무너무 행복했고, 무조건 꼭 다시 오고싶어요!!! 스파도 너무좋은데 객실은 독채가 아니라 조금 기대를 내려놓고 갔는데 진짜 너무 좋았어오ㅠㅠ 숲뷰 힐링 그자체❤️</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>완전 굿굿 꼭 오션뷰로 하세요 ! !!!!!곽지해수욕장 바로 앞이에요!뷰 짱 좋고 너무 맘에 드는 숙소였어요 !  침구도 깨끗하니 보송보송하고 사각사각 바스락 소리나는 딱 호텔 침구라 저는 좋았는데 귀 예민한 부모님은 시끄러워서 잠을 못 주무셨다네요ㅠㅠ ..ㅎㅎ 예민한분들 참고하세요그리고 주변 식당들이 일찍 문을 닫아서10분정도 걸어가서 포차에서 맥주 한잔과 식사했네요! 저는 완전 만족하고가요 !!!</t>
+          <t>방은 생각보다는 작은데 딱 4명이 자기 좋았어요겨울에 눈 보면서 하는 스파는 최고였어요룸컨디션도 좋고 뷰는 진짜 좋았어요위치는 진짜 산속에 있어서 차 없으면 오기 힘들거같긴한데 다음엔 부모님 모시고 재방문 해야겠어요</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -744,7 +744,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>방사진은 미처 못찍고.테라스뷰 좋아요.해수욕장이 가까워서 선택했는데 너무 좋네요.직원분들 너무너무 친절하셔서 반했어요.바닥이 카페트인걸 좋아하지 않아서 좀 불편했어요.이건 제대로 확인안한 제불찰이구요.욕조는 없지만 화장실이 커서 씻고할때 편했어요.그치만 칸막이 밑으로 물이 튀어서 세면대밑쪽이 물바다가 됐는데 경사가 없었나봐요.아침까지 물이 흥건하더라구요.어매니티도 충분하고 만족해요.싫어하는 카펫바닥임에도 재방문의사 있어요.</t>
+          <t>직원분에게 감동해서 또 가고픈곳이 되었어요!!!지갑을 어딘가서 잃어버려서 퇴실한룸. 로비 아님 주차장일거라 알려드렸는데 10분만에 콜백와서 주차장서 찾았다고 알려주시고 택배로 보내주신다했어요 이름도 못여쭤봤는데 27일 오전11시30분즘 전화응대해주신 여성직원분 정말 최고에요!!!</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -756,7 +756,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>간만에 다시 들른 마레보비치호텔. 체크인/입실을 밤10시에 하는바람에 1층에 배정되어서 살짝 아쉽긴 했지만. 그래도 오션뷰는 좋아요~ 공영주차장 일부 공사중인 거 빼면 뷰는 이쁩니당ㅎㅎ 객실도 대체적으로 깔끔한 편이고 직원분도 친절하고 좋습니다. 다음에 제주 오게되면 또 들릴께요~!</t>
+          <t>숙소 침구 편안해서 숙면했고, 욕실에 물때 하나없이 깨끗했고 난방온도 너무 덥지않아 좋았고 이용하는 시설마다 직원들.침절하시고 산속 스파는 너무 좋고.. 잊지못할 1박입니다 ^^</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -764,11 +764,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>호텔에서 도보 2분 거리에 바다가 있어요! 바깥에 바로 편의점이 있고 주차가 지상과 지하가 다 있어서 불편함이 없었어요! 오션뷰 객실로 업그레이드도 해주시고 프론트에 계시던 중년 남성 두분, 오전에 계시던 여성분 모두 다 정말 친절하셨습니다 너무 깍듯하셔서 같이 90도 인사 하구 나왔네요 😂😂 객실 내부는 약간 호+모텔 느낌이지만 1박 투숙하기엔 편했습니다!</t>
+          <t>일찍도착해서 얼리버드체크인 가격이있어도 직원분이친절하게 산뷰로해주시고 객실에들어서니 계곡물소리 깔끔한침구 넘좋네요헤브나인스파로 몸을녹이고 뷰좋은곳에서 숲멍하고 좋은칭구와 좋은곳에서휠링했네요</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -780,7 +780,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2박 디럭스트윈 예약하고 당일 방문했는데 사장님께서 성인 4명이라고 (아무 조건없이 ㅎ) 스위트룸으로 업그레이드해주셔서 너무 깨끗하고 편하게 지내고 왔습니다.곽지해수욕장 바다도 보이고 호텔에서 밤에 가보니 바로 앞이라서 야경 즐기기에도 넘 좋았습니다.가족 여행 즐거운 추억이 되었네요.감사드립니다. 번창하시길 기원드립니다^^</t>
+          <t>대가족 함께 여행했습니다회사 법인회원권 있는 형제가 있어 한동 빌리고, 제가 여기에서 별도로 한동 빌렸는데 너무 만족스러웠어요숲속에서 쉬엄쉬엄 산책을 즐기며 힐링의 시간 가졌습니다리솜계열 다 다녀봤는데 제천이 젤 좋네요ㅎㅎ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>체크인 전에 짐보관 가능해서 덕분에 편하게 여행했어요! 프론트 직원분들도 친절하시고 꼼꼼하게 안내해주셔서 불편한점 없이 이용했습니다.곽지해수욕장까지 굴러가도 될정도로 코앞이라 바다구경도 실컷하고 오션뷰 묵었는데 애매한 오션뷰 아니고 정말 바다가 바로 보여요!그리고 기분탓인지 모르겠는데 더블침대가 다른 숙소에 비해 조금 더 큰 느낌이였어요 둘이잤는데도 하나도 안좁고 넉넉했습니다.수건도 큰사이즈 / 작은사이즈 각각 인원수대로 비치해주셔서 넉넉히 사용했어요.침대 사이에 콘센트 없는거랄 방에 벽쪽으로 붙어있는 붙박이테이블(?) 외에 따로 뭔가 먹거나 할 수 있는 테이블이 없어서 아쉽긴했는데 그 외에는 컨디션 다 좋아서 만족스러웠습니다! 다음에 또 묵고 싶은 숙소였습니다!! 마레보비치 리조트랑 호텔 두개 있어서 택시타고 갈때 헷갈리지말아야겠더라구용</t>
+          <t>다양한 스파와 놀거리가 최고였습니다!!!! 잊지 못할 추억을 만들었어요. 다만 다 끝나고나서 조금 몸이 간지러웠네요.ㅠㅠ 그래서 가실 분들은 꼭 전신 수영복 추천합니다!!! 또 나중에 방문 의사 있어요. 몸 노곤해지고 편하고 아주 좋습니다~~</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>이런거 잘 안쓰는데 숙소위치가 해변앞이라 걱정햇는데 관리 진짜 잘되있어요 가성비도 좋고 해변도 가까운거도 좋고 동네 자체가 이쁘고 맛집도 많아요 현재 신*월*인데 가격은 반값인데 다음엔 마레보호텔 쭉 있으려고요 추천합니다</t>
+          <t>친구들과 제천 리솜에 가고 싶어서 계획한 여행이었어요. 포레스트와 레스트리 고민하다가 이번엔 레스트리에서 머물렀는데, 깔끔하고 조용하고 편안해서 친구들 모두 매우 만족해했어요. 다음엔 포레스트에 도전! 산책길도 너무 좋았고, 안에 편의시설이 잘 되어 있어서 편리하게 이용했어요. 다음엔 가족들과 함께 가려고요.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>호텔 뷰는 말할거 없이 좋고 호텔바닥이 온돌이라 히터기처럼 소음이없고 눈이건조하지않아 아주 좋았어요.하지만 샤워할때 물이 안빠져서 식겁했어요.다좋을순 없지만 운이없다기엔 심각한문제라 다소 아쉬웠네요.그래도 주변식당가도 많고 산책하기에도 아주 좋은 숙소라 생각합니다.가성비 굳~</t>
+          <t>리조트가 고즈넉해서 조용히 휴식하기 좋았습니다리조트내에거 카트가 없으면 이동이 불편하고 식음업장이 몇개없어 선택의 폭이 좁습니다 스파시설이 좋아 아이들이낯가족들하고 가기 좋을것같어요 조용히 휴식을 원하는분들이라면 꼭 가보세요!</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>곽지해수욕장 코 앞에 있어서 놀기 너무좋아요.놀다가 조금 휴식하다가 또 놀고 하면되서 아이랑 놀기가 너무 좋았어요. 숙소도 깔끔하고, 화장실 바닥이 미끄럽지 않고 금방마르는 재질이라 습하지 않고 좋네요. 주차장이 지하인 것도 너무좋아요 비올때나 너무 더울때 주차장이 지하에 있어서 참좋았어요.근처에 애월빵공장이나 버거리도 있어서 너무 좋았습니다</t>
+          <t>날이 슬슬 추워지니 예약하기 힘들었지만 역시 온천은 부모님이 좋아하시네요! 방두개 화장실 두개 객실 너무 좋았음! 대체로 깨끗한 객실에 친절한 직원까지 좋았습니다! 다만 부대시설이 해브나인 말고는 약하긴 해요ㅠㅠㅠ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -840,7 +840,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>객실에서 바라보는 오션뷰는 진짜 너무 환상적이었어요직원분들도 친절하시고객실은 우선 화장실은 수압이 약한거 말고는 전반적으로 좋았고객실은 커텐이 (밑에)  곰팡이 핀거같이 시컴하고 곳곳에 오래되보이는 오염물질이ㅜㅜ난방은 히터였는데 건조해서 베란다문을 살짝열고 잤어요!!전반적으로 나름 만족한 숙소였습니다.</t>
+          <t>가족여행으로 선택한 제천 레스트리 리솜리조트에만 있어도 힐링이 되는 곳이에요특히 스파와 인피니티풀이 유명한 곳인데요저희는 야간입장으로 여유롭게 즐기고 왔어요!부모님 모시고 가기 좋은 숙소여서가족여행 계획하신다면 추천드립니다!</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>숙소가 깨끗하고 직원분들도 친절했고 무엇보다 뷰가 너무 좋았어요! 바로 앞 곽지해변도 예쁘고 주변 카페나 술집들도 분위기 있어요. 또 방문하고 싶네요~ 다만 화장실은 문이 샤워부스문 같아서 방음이 안된다는 단점이.. 다른건 다 좋았습니다~</t>
+          <t>가족들과 좋은시간 보내고 왔습니다.부대시설 좋고 수영장도 좋습니다.앞으로도 종종 이용할 것 같습니다!날씨 좋을 때 한번 더 방문할께요!</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -864,7 +864,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>여사장님이 엄청 밝으십니다.진짜 보는사람 기분 좋아지는 느낌을 받았습니다.시설 또한 아주 깨끗하고 뷰가 정말 좋았습니다.앞에 편의점도 가깝고 곽지해수욕장앞이라 뷰도 좋은점 참고하시고 다들 예약가즈아 ㅎㅎ사장님 생각나서 리뷰남기러 들어왔네요ㅎㅎ</t>
+          <t>너무 좋아요 입장할 때 느껴지는 리솜만의 향기부터 다 맘에 드는데 제가 이용했던 48동 3호(S30) 여기 싱크에서 악취나는거랑 침실에서 큰 개미 나온거 그리고 객실에 잔 종류가 좀 부족한거 빼면 완벽합니다. 😎👍👍👍👍👍</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>일단 너무 넓고 모던한느낌 좋았어요역시 바다뷰...아침에 뛰노는 고양이와 개도 구경 잘 했습니다 ㅎㅎ욕실에도 물때하나없이 깨끗했고 수건양도 넉넉했어요소음도 없었어서 재방문의사 있습니다</t>
+          <t>웰컴 향기부터 룸 컨디션, 직원 친절, 온천까지 모든게 완벽했던 포레스트 리솜이였어요. 날이 풀린다면 봄에도 한번더 올 예정입니다</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -884,11 +884,11 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>해변 바로 앞이라 해수욕을 즐기고 돌아온 손님들에 의해 호텔 로비랑 엘리베이터가 지져분해지기 쉬운데 계속 청소를 하시더라구요. 그 부분 역시 감동.</t>
+          <t>리조트 시설 및 룸컨디션은 최고였습니다.다만 리조트 자체가 크다보니 모든 부대업장이 친절하지는 않습니다그걸 감수하고서라도 다음에 또 오고싶을만큼 즐거운 경험을 많이 했습니다~!</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -900,7 +900,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>가성비 좋은 숙소였어요. 사진보다 규모가 작은거 같긴 했지만 관광하고 잠만 잘거라 상관 없었어요.직원분들이 모두 친절하시고 좋았어요.객실에서 바다도 잘 보이고 편의점도 가까이 있어 편했어요.</t>
+          <t>체크인을 4시에해서 뷰 좋은 방들이 마감이라 아쉬웠어요. 숙소 깨끗하고 인테리어 신식이라 좋았습니다.산책해보니 포레스트동 독채가 진짜 숲속이라 좋아보이더라고요 다음번엔 포레스트 빌라 묶고 싶네요.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -912,7 +912,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6명이서 갔는데 방3개라 딱 좋구 너무 좋았어여 뷰가 진짜 좋구요 청결해요 4월말에 일반 객실 와보고 괜찮아서 스위트 객실 예약했는데 스위트는 진짜 좋네여 비싼 값을 하네요 담에 기회되면 또 스위트객실 이용하고 싶어요</t>
+          <t>제주도 가려다가 결항으로 급하게 당일예약하고 제천 여행갔는데 스파도 좋고 너무 좋았습니다! 다만 스파는 겨울에 가시려면 야외스파가실때 신을 아쿠아 슈즈 꼭 챙기세요^^,,,</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -924,7 +924,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>엄청 친절합니다.친절한 만큼 숙소도 좋을거다 예상했는데예상대로 몹시 좋습니다. 방문객 마저 기분 좋아지게응대해주시는 곳은 너무 오랜만이라 쌍따봉 드립니다.재방문 의사 있습니다.</t>
+          <t>레스트리 체크인 왼쪽에서 해주신 여성분 완전 친절하셨고 힐링을 목적으로 숲캉스 온거였는데 잘 즐기다갑니당 수영장은 생각보다 아담했어요 &gt;&lt; 사진은 객실 거실뷰 727호 방입니당</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -936,7 +936,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>직원분들이 엄청 친절하시고호텔 위치, 분위기 다 최고입니다.가족여행으로 갔고 다시 또 애월을 가면 무조건 여기서 묵을 것 같아요</t>
+          <t>이번에 첫 방문이었는데 모든 면에서 정말 마음에 들었습니다.  다음번에  가족 여행 으로 재방문의사 100% 입니다</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -944,11 +944,11 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>바다도 잘 보이고 좋았습니다.냉장고는 냉동까지 되는것이라 더 좋았습니다. 아쉬운 점은 타월이 한 장은 그래도 하얀 편인데 다른 한 장은 회색이어서 사용할까말까 컴플레인을 해야하나 고민이 될 정도였습니다.</t>
+          <t>근래간 리조트중 가장단연최고 직원분들 대응너무친절하고빨라서 불편함없이 휴가보내고옵니다 절경도너무좋고 공기 산책 스파 모든게완벽한 최고의휴가 엿습니다 감사합니다</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -956,11 +956,11 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>스탭분들 친절하시고 편하게 이용했어요테라스 딸린 방 이용했는데 테라스쪽이 구멍뚫린 바닥이라서 거기서 냄새가 좀 나는거 같더라구요객실에서도 습기 때문인지 좀 쿰쿰한 냄새가 난다고 할까요ㅜㅜ 그것만 제외하면 편하고 아늑하고 제주를 충분히 즐길 수 있었어요!!</t>
+          <t>독태 빌린기분에 전동카트 까지 잘 되어있어서 1박 푹 쉬고 왔습니다! 산책길 걷는데 너무 이쁘고 행복하게 지내다 왔네요! 또가고 싶습니다~~ 조식은 이용못했지만 조금 비싼것같아요~</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -968,11 +968,11 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>매번 제주 여행때마다갔는데, 이번엔 청소도 안된 방을 줘서 불쾌했어요~비슷한 방이 없어 업그레이드 시켜줬지만, 조금 실망이었는데 방을 보고 기분이 풀렸네요~</t>
+          <t>스파, 마묵라운지 등 좋고 아이들을 위한 음료수 등이 있어요 숙소는 포레스트라 숲속 산장 느낌인데 오래되어서 깨끗한 편은 아니에요....그래도 공기좋고 산속에서 힐링하는 느낌이었습니다</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -984,7 +984,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>너무좋았어요 룸컨디션도 깨끗하고 좋았고 감각적인 인테리어와 노을지는 해변뷰도 너무 멋졌습니다 곽지해수욕장이 코앞이고 주변에 맛집도 꽤 잇엇고 도보5분거리에는  무인제주 해변뷰 칵테일바도 있어서 밤에 다녀오기 좋앗어요 :)</t>
+          <t>시설이 깨끗하고 직원들도 친절하고 특히 수영장 아주 좋아요~~^^객실뷰는 크게 뛰어나지는 않지만 전체적으로 힐링하기 아주 좋은 곳인듯합니다~~조식도 가격은 좀 쎄지만 아주 맛나네요~~</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -996,7 +996,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>테라스도이쁘고 방도깔끔하고너무좋았어요ㅎㅎ 근데 체크인한날은 날씨가정말안좋았는데떠나는날해가쨍쨍이더라구요ㅠㅠㅋㅋㅋ 짐정리하면서더있고싶다는생각뿐일정도로너무만족한곳이었습니다!!</t>
+          <t>시그니처 풀도 좋았고 평일이아 사람이없어 쾌적했음. 친절하며 부대시설 깔끔. 또 가고싶어요</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1004,11 +1004,11 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>곡지 해수욕장이 바로 앞에 있고 바다뷰라 아주 좋아요 편의점도 가깝고 주변 맛집도 많고 만족합니다. 4인가족으로 가니 객실이 좀 좁아서 아쉽긴했지만 만족스런 하루 였습니다 ^^</t>
+          <t>생각보다 숙소 크기가 크진 않다고 느껴졌어요. 하지만 깨끗이 관리되고 있고 스파 시설이 온 가족이 즐기기에 적당하여 좋습니다. 조식도 가격대비 나쁘지 않았습니다</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>제주 갈때마다 들리는 곳입니다. 이번에 리모델링을 하셔서 로비도 바뀌고 욕실도 바뀌고 더 좋아졌네요. 방에 공기청정기까지~ 직원분들도 넘 친절하셔서 아주 편하고 즐겁게 있다 왔습니다. 담에 제주갈 때 또 이용하겠습니다^^</t>
+          <t>어머니칠순겸 같이다녀왔는데 가는날 눈이내려서경치가예술이였네요 침대도편안하니 푹쉬다왔습니다다만 음식값이 사악하네요</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>아침에 일어날 때마다 바다가 바로 보여 기분이 저절로 좋아질 만큼 좋은 기억으로 남은 여행이었습니다.호스트분들 모두가 친절하셔서 다음번에도 제주도를 여행한다면 들리고 싶은 숙소입니다!!</t>
+          <t>방도 생각보다 넓고 쇼파에 티비에 편히쉬었어요 다만 밤에 추웠어요  스파도 저녁에가서 사람별로 없어서 편히 썼는데 야외 엄청 추워요 소리지르고 다닐만큼 다른분들도요 ㅎㅎㅎㅎㅎ 또 가고 싶을만큼 만족스러운 곳입니다</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1040,11 +1040,11 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>지인이 방문해서 호텔을 예약해줬는데, 이불이 넘넘 푹신해서 좋았다고 하네요~~ 그런데 벌레가 있어서 깜짝 놀랐대욯ㅎ 성수기라 객실 교환도 안되고ㅠㅠㅠ 에프킬라 하나 받았다고 합니다ㅠㅠ 암튼 바로 앞이 곽지해수욕장이라 그게 가장 만족스러웠다고 하네요!!</t>
+          <t>이번에는 조카가 독감에 걸려서스파도 못하고 그냥 와서 아쉬워요 ㅜ패키지라 이용못한건 다른걸로바꿔주는 시스템도 만들어주셧으면 좋겠어요 역시나 리솜은 최고입니다 ㅎ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1052,11 +1052,11 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>오션뷰를 너무 기대했는데 정말 좋더라구요 !! 인테리어도 이쁘고 깔끔한데 침구도 편안해서 푹 자고 가요 ㅎㅎ대신 치약칫솔은 제공안하니 가져가야하고, 트리트먼트라고 써있는 통에 로션이 넣어져있습니다 참고하시길</t>
+          <t>조용하고 룸 컨디션좋고 전반적으로 만족합니다다만 쇼파에서 조금 냄새가 났고 연인이나 나이드신분들보단 아이있는 가족단위가 더 좋은곳같네요</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>친구들이랑 애월 근처로 알아보다가 마레보에서 숙박하게 되었어요 :) 업그레이드 해주셔서 좋았구요 전체적으로 깔끔해서 좋았습니다 침대는 원래 떨어져있는건데 저희가 붙인거에요다 좋았지만 한가지 아쉬웠던건 넷플릭스가 안돼요! 그거 빼고는 다 좋았습니다!!♥️</t>
+          <t>숲속에서 완벽하게 힐링할수 있는 2박 3일 이었습니다 해브나인, 그리고 단락에서 기족 사진, 별똥카페등 리조트 안에서 볼거리 놀거리가 많아요</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1076,11 +1076,11 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>아침에 일어나자마자 바다풍경 너무 예쁘네요 다 새거는 아닌데 청소상태 너무 좋아요!! 바닷가 바로 앞이라 아이가 아침에 모래놀이 하고 씻고 체크아웃하니 제일 좋았다 하네요 추천요!!</t>
+          <t>이름그대로 숲에 들어온 느낌이고 안에서 불편한 점은 하나도 없네요~ 다만 나갔다오기엔 시간이 좀 걸리는건 감수해야할거같아요~담에도 방문하고 싶습니다~</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>이번 겨울 가족여행 해비치호텔에서 보냈는데아이들 놀거리도 많고직원들도 친절해서편안히 잘 쉬다갑니다너무 좋아요</t>
+          <t>그냥 최고입니다~~ 가을에 가면 특히 제일 멋질것 같네요!조식은 최고 그 자체입니다!! 강추</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>작은 방이지만 있을거 다있고, 실속있었으며친절도 매우 좋고,주변 식당도 적당히 있고, 배달도 되서 편했습니다.먼지가 좀 있어서 청결도는 조금 아쉬웠습니다!</t>
+          <t>G40타입은 처음 가봤는데, S30과 넓이는 같지만 어메니티 등이 다르고, 식탁 인용이 다릅니다 ㅋㅋ제천레스트리는 항상 좋아요가족과 잘 휴식했습니다^^</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>일단 뷰가 넘 좋아서 만족합니다근처 식당 편의점이 가까이에 있어 편리했어요토끼띠 인증이 있어 커피랑 빵도 서비스 받았구요맛도 좋았답니다뷰는 진짜 좋아용~~^^ ㅎ</t>
+          <t>가족여행- 부모님 동생가족들과 여행다녀왔어요 풀장은 물이 따뜻해서 아기들도 재미있게놀았고 룸컨디션도 괜찮아서 어른들도 만족했어요 무엇보다 자연을 가까이 잘 즐기고 왓어요</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2박했습니다. 청소도 잘되어있었어요  다만 제가 묵은 곳에서  주차장까지 가기좀 불편했어요.. 그거외엔 다 만족합니다. 특히 직원분들 정말 친절하십니다.</t>
+          <t>매번 가는 좋은 휴식처입니다. 직원들 응대가 보통인 곳이라 그 점은 아쉽지만 자연 속에서 쉴 수 있어 좋아요</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>오션뷰 너무 좋았고 바다랑 가까워서 너무 좋았습니다!! 바로 앞에 편의점도 있고 카페들도 있어서 좋았던 것 같아요 ~~ 직원분들 모두 친절하셔서 기분 좋게 다녀왔습니다! 재방문의사 있어요 😄</t>
+          <t>객실 컨디션 좋았고 조식도 여러가지로 꽤 괜찮았습니다.눈덮인 산을 바라보며 하는 스파도 좋았어요계절별로 와보고 싶네요</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>조용하고 곽지해수욕장 안에 있어서 뷰도 좋고요.공항 가까이 있어서 접근성도 좋습니다. 관리가 아주 잘된 느낌이에요~ 바로 앞에 편의점도 있고 완전 만족해요!!!</t>
+          <t>스파 이용했고 숙소는 업그레이드 되서 너무 좋았어요.직원들은 전체적으로 다 친절했어요.내부에 식당도 잘 구비되어있어서 식사에도 어려움이 없었어요. 다음에 또 가고 싶네요</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>저녁 아침 직원분들 정말친절하셨어요 웃는얼굴밝은목소리 ㅎ여름에가면 해수욕장바로앞이라 좋을거같아요</t>
+          <t>직원분들도 친절하고 숲뷰도 좋고 숙소도 깨끗하고 좋았습니다, 스파는 주말이라 사람이 많았는데 나중에는 v탑스파 예약해서 프라이빗 하게 즐기는것도 좋을거 같아요</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1172,11 +1172,11 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>위치도 너무좋고 프론트직원분들도 엄청 친절하네요 2박했는데 잠깐 비운사이에 청소도 깔끔히 해주시고 침대도 편해서 좋네요3성급이라고 힌지만 다음에도 또 이용하고 싶네요</t>
+          <t>자연속에서 잘 쉬다가 왔어요~숲속이라 객실은 조금 꿉꿉해서 아쉬웠지만 부대시설 깔끔하고 조경도 마음에 들었어요단풍든 가을에 가면 더 좋을 것 같아요</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>오션뷰 가운데 나무가 있어서 처음에는 잉?! 싶고 아쉬웠지만 은근 왼쪽 오른쪽 나눠서 보는 맛이 있더라구요ㅋㅋㅋ 객실 굉장히 깨끗했고 직원분들이 친절하게 응대해주셔서 기분이 좋았습니다ㅎㅎ</t>
+          <t>두번 째 방문한 리조트 너무 뷰가 좋아서 힐링을 제대로 하고 가요 🫶 바쁜 도심에서 지쳐가는 현대인들에게 탁월한 휴식처</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1196,11 +1196,11 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>일부로 잡은 오션뷰인데 비가와서 아쉬웠어요 ㅎㅎ청결은 청소하시는 분께서 깔끔하게 해 주십니당침구 오염 있어서 교체 요청해드렸는데 확인 후 청결하게 바꿔주셨어요! 감사합니다</t>
+          <t>노천탕도 운치 있고 좋았고 객실도 너무 깔끔하고 침구도 너무 편해서 푹 쉬다 왔어요~!힐링 되는 가족여행 되었네요~^^</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>간만에 편안하고 아름다운 바다를 보면서 휴식을 보낸곳인것 같습니다다음에 꼭 다시 방문해서 즐거운 여행을 또 한번 즐기고 싶습니다</t>
+          <t>룸이 전체적으로 깔끔해서 너무 좋네요 :)방3,거실1,화장실3이라서 매우 좋고노래방,편의점,bbq,스파 안에서 해결할수있어서 편리하네요</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>곽지해수욕장 옆에 위치하고 있어 창문 너머 보이는 바다풍경이 일품.깨끗하고 시설이 잘 되어있어 만족한 여행이었습니다.다시 머물고 싶은 호텔</t>
+          <t>처음가보는곳인데 직원들 친절하고 방컨디션 청결도 다 최상이에요다음에 또 이용 의사 100%</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>생각지도 못했는데 객실을 업그레이드 해주셔서 바다 보이는 방에서 너무 편하게 잘 쉬고 왔어요ㅎㅎ그리구 바로 앞이 곽지해수욕장이라 산책하기도 좋네요~~🥰</t>
+          <t>정말 만족스러운 가족 여행이었습니다.스파 시설도 다양하고 직원분들도 친절하시고 ㅎㅎ부모님들 모시고 재방문 의사 있습니다. 🥰</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>공간은 많이 넓지 않지만 다른 장점이 많은 숙소였어요. 뷰가 좋아 테라스에서 앉아서 바다를 보고 있는 걸로도 충분히 만족할만한 곳이었습니다. 인테리어도 예쁘고 피자 룸서비스도 맛있었어요.</t>
+          <t>숙소 상태가 청결하고 침구세트도 푹신하였으며 전반적으로 매우 만족하였습니다.붉게 물든 단풍과 사이로 산책로가 잘 구비되어 있었습니다.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>아주 친절하셨고 3연박 했는데 불편함 전혀 없었습니다. 바로 앞 바다도 예쁘고 바로 옆에 편의점도 있어요. 다음에도 또 오고싶네요</t>
+          <t>아이와가기에 최고의리조트 다만포레스트는 카트를타고 경치를구경하기좋으나 부대시설까지 다니기에는 번거로움이있어 다음에 간다면 레스트리를 이용할것같습니다.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>위치가 곽지해수욕장 바로 앞이라 편했고 낮에는 카카오택시도 잘 잡혀서 좋더라구요 객실 크기는 사진이랑 똑같았어요</t>
+          <t>돌 갓 지난 아기와부모님과 함께 방문했어요전경도 좋고 시설도 깨끗하고 편리했어요헤브나인스파는 진짜 너무 좋네요최고의 휴가였어요!</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>아주 편하게 잘 이용하고 갑니다!🧡🫶🏻🧡직원분들 쏘 카인드하시고 좋았어요!전신거울이 없고 고데기하면서 거울을 볼 수 없는 콘센트 위치라 조큼 아쉬웠습니다!</t>
+          <t>처음가봤는데 객실도 깔끔하고 스파도 좋았어요!스파 사람이 너무 많아서 스톤그거는 이미 마감됐지만요ㅋㅋㅋ뷰도 없다고 들었지만 전 괜찮았아ㅣㅓ요</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>스위트객실 이용했는데 가격대비 너무 만족했습니다.객실 컨디션도 완벽했고 특히나 곽지해수욕장이 보이는 뷰가 끝내줬습니다.재방문의사 120% !!!!!!!</t>
+          <t>시설 친절도 다 좋았어요 다만 리조트 특성상 가족단위로 많이 와서 커플 단듈끼리는 비추입니다. 애기들이 엄청많아요ㅠ 암튼 가족끼리는 강추 커플끼리는 비추입니당</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1304,11 +1304,11 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>다시 방문 의사드는 곳입니다특히 여 직원분 친절함은 굿!!테라스 뷰는 또 좋아요ㅎ테라스 중문이 좀 잘 안열림</t>
+          <t>청소상태 깨끗하고경치는 서비스 좋은추억 많이 만들고 왔어요.가족단위.친구들.연인끼리 모두모두 좋아요~</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>안내하시는 직원 분들 너무 친절하고 좋았습니디.방이 좀 좁은거 빼면 만족스러운 여행이었습니다. 뷰도 좋고, 동네도 한적하고 너무 좋았네요</t>
+          <t>최강 한파에 떠난 여행이었지만, 지인들과 좋은 추억 쌓았습니다. 1박만 하기엔 너무 아쉬웠던 숙소였네요.6명이 넓게 사용했던 식탁과 의자 편해서 좋았고 조명도 조화로웠습니다. 블루투스 스피커 넘 탐날만큼 훌륭했구요.카트 이동도 생각보다 많이 대기않고 잘 다녀왔어요.난방 완벽~^^</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>바로 앞이 곽지해수욕장입니다!!침대에 누워서 바다멍때리기 너무 좋아요~침구가 딱딱한거 빼고는 모듀 만족이었습니당</t>
+          <t>좋은경치 깔끔한시설에 즐거운시간보내고왓어요~~다만 아기용품 대여가능한데 다 추가금이 있어서 아쉬웠어요ㅜㅜ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>곽지해수욕장을 온다면 무조건 여기에요 작년에 이어 두번째 연박했습니다. 해수욕하고 놀며 쉬기에 최고입니다.</t>
+          <t>부모님 모시고 가거나 아이와 함께가면 정말 좋을 것 같아요. 수영장과 스파시설도 잘 되어있고 레스토랑도 많아서 행복한 시간 보냈습니다.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>방이 조금 작다는 생각은 들었지만 청결하고 오션뷰에 통창이여서 아주 좋았습니다. 직원분들도 너무 친절하시고 아침 조식도 아주 좋았습니다.</t>
+          <t>7인실 방에서 친구들과 모임했습니다 쾌적하고 공기좋고 경치 좋아서 잘 쉬었습니다 다만 스파는 성인들이 놀기에 규모가 크진 않습니다 겨울이 좋을듯</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>직원분이 너무 친절하구 이가격대에 이퀄리티 오션뷰는 장난아닌 가성비에요. 냉동실이 살짝 아쉬운것 빼고는 다 조았어요!!</t>
+          <t>어제 지었나  싶을 정도로  너무 깨끗했습니다  가격이 좀 비싸긴하지만  가족들 모두  좋다고 만족 했습니다 봄에 또 가려구요~^^</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1376,11 +1376,11 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>전망이 좋아요 바로  앞에  바닷가라 언제든디 갈수 있고 조용해서 다음엔 오래머물면서 힐링할까 합니다</t>
+          <t>가족여행좋은추억남기고온거같아요!사람이많긴합니다!!일요일에갔는데정신없었구요방은정말따뜻해요~ 잘쉬다갑니다!</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1층에 프론트와카페가같이있어서좋아요!!!뷰도넘좋구 바닐라라떼도맛있었어요ㅇㅅㅇ온돌방식이라 방안에서조절가능한것도 너무좋더라구요</t>
+          <t>정말 힐링 그 자체 할 수 있는 곳이예요숙소도 들어가자마자 엄청 따뜻해서 좋았고객실 너무 깨끗하고 좋아서 다들 감탄했어요산책하시 너무 좋고 스파도 즐길 수 있어서 만족스러웠습니다</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1400,11 +1400,11 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>곽지에서 숙박은 처음인데 나름편의시설도 있고 식당도있고 괜찮더라구요~~!!바다까지 접근성이 좋아 여름철 숙소로 추천해요~~!!</t>
+          <t>부모님 모시고 다같이 가족여행왔는데 다들 만족하는 숙소, 스파 여행이라 다음에 또 올 예정입니다. 깨끗하고 시설도 다 잘갖춰져있어서 좋았어요^^</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>버스 접근성도 좋고 택시도 잘 잡히는 위치입니다. 바다가 보이는 좋은 조망과 깔끔한 어메니티영어도 가능해서 호텔로서 딱 이었어요</t>
+          <t>객실이 깨끗하고 따뜻했어요헤브나인 스파도 좋았어요설에 폭설이라 걱정했는데 설경을 바라보는 야외스파가 정말 만족스러웠어요다음에 또 재방문하고 싶어요</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>제주도 여행중  최고의 호텔 이였습니다직원분들 매우 친절 하고 룸컨디션도 매우 좋았습니다강추드립니다</t>
+          <t>넓고 전망좋습니다싱크대와 접시등 간단한집기들이 있어서 과일이나 간단한음식 등 먹기좋아요추천합니다</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1436,11 +1436,11 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>직원도 친절하시고 냄새도 안나고 청결하고모든 면이 마음에 들어요나중에 또 애용하고싶어요~~~~</t>
+          <t>아무래도 산속에 있다보니 왔다갔다하기는 조금 힘들긴 해요! 그렇지만 그거 제외하고 스파가 넘 좋았습니다ㅎ다만 스파랑 찜질방 안에 스낵코너나 식당이 좀더 활성화됐으면 좋겠어요ㅠㅠ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>직원분들도 너무너무 친절하시고 객실도 너무 훌륭했어요 오션뷰도 너무 좋았고 통창으로 탁트인 전망이 너무 좋았네요 다음에도 이용 할 생각있어요~</t>
+          <t>침대가 너무 푹신하고 편해서 꿀잠 잘수 있었고 객실 내부도 깨끗하고 쾌적했어요~ 조식도 너무 맛있어요!</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1460,11 +1460,11 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>괜찮은것 같아요 단지 침대 옆에 책장이 많이 거슬리고 구멍이 중간 중간 뚫려있어서 신경쓰이는거 말곤 완벽했어요</t>
+          <t>침구 너무 폭닫하고 좋아서 자는데 가분이 ㅈㅎㅎ았어요. 뷰도 좋고, 직원분들이 너무 친절하셔서 또 오고싶어진 숙소였어요^^</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>친절 하셔서 너무 좋았어요 아쉬운건 너무1층이라 창문을 거의 커튼만 치고 지낸게 아쉬워요 청결도는 너무좋앗고 요청하지않아도 어메니티 채워주셔서 좋았어요!</t>
+          <t>부모님 모시고 갔다왔는데 카트로 이동해야하는 것 말고는 크게 불편한점이 없었습니다보일러도 잘들어오고 수영장도 좋았어용근데 안에 있는 모든 음식이 너무 비쌈... ㅋㅋㅋㅋㅋ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>뷰가 정말 좋았어요~연박했는데 청소도 잘해주시고 친절해요^^ 다만 이튿날 룸의 와이파이가 잘 안잡혀서 옆방걸로 이용했어요^^,,</t>
+          <t>기대했던 해브나인은 생각보다 쏘쏘였지만 숙소는 좋았어요. 산책하기 좋아요. 리조트 내 식당 비싸지만 고급지고 맛났네요.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>직원분들 친절하셔서 너무좋아요!!시설도 깔끔하고 조용하니 진짜 잘쉬다갑니다ㅎㅎ다음 제주여행도 다시 방문할게용</t>
+          <t>다 좋은데 카트를 타고 계속 이동해야해서 그게 조금 불편햄ㅅ어요 그거빼곤 나머지는 다 좋았습니다 ~</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1508,11 +1508,11 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1층인데도 반층이 높아서 좋았어요~사진처럼 바다도 보이고~직원분들 친절하셨어요~</t>
+          <t>가족과 함께가기 아주좋은 숙소였습니다스파도 이용하고 조식도 맛이 괜찮았어요리조트안에서 많은걸 할수있어 좋았어요무엇보다 숲속에있어서 맑은공기 마시니 힐링되는 느낌이였습니다^^</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>나쁘진않아요. 바로앞 바닷가 먹을게 다있어서 편하긴해요. 더러운곳보단 돈좀더주고 오는게낫음</t>
+          <t>진짜 가족들이랑 가볼만해요~^^ 저희는 오후에 늦게 도착했는데 오전에 미리가서 체크인하구 스파 꼭 이용해요!</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>곽지해수욕장에서 아주 가까워서 물놀이 하러가기 딱 좋았습니다! 직원분들도 친절하시고 깔끔한 숙소에 바다뷰도 좋았습니다~~~</t>
+          <t>자연속 휴가를 원한다면 여기로 가세요.취사가만되는건 아쉽지만 그래도 쉬고 오기에는 넘 좋은 곳입니당~</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>티비가 ott가 안된다는점음 쬐금 아쉬웠지만 전체적으로 깔끔하고 만족스러운 숙소였어요!!</t>
+          <t>체크인데스크에서 정말 친전하게 가장 좋은방을 추천해주셨어요 갈때마다 깨끗하고 쉬기에 좋습니다 쿠폰써서 합리적으로 예약했네요</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>제주에서 묵은 첫 호텔.덕분에, 제주에 대한 첫 인상도 애월에 대한 첫 인상도 너무 좋았습니다.</t>
+          <t>부모님이랑 아이 데리고 가기 정말 좋은 곳이에요~둘째 태어나면 또 가려고요!스파도, 숙소도, 산책길도, 조식도 다 만족하고 왔어요~</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>친절한직원과 하루하루 깨끗이 청소해주시고 항상 좋은 미소를 띄이며 인사해주시셔서 너무 좋앗습니당 ㅎㅎ</t>
+          <t>시설이 고급스럼고 체크인 할때 친절한 설명도 좋았습니다. 스파시설도 깔끔하고 가족단위 이용하기 좋았습니다.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1580,11 +1580,11 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>곽지해수욕장이 바로 앞이라 물놀이하기에도 좋고 주변에 편의점이랑 치킨집있어서 오가며 들르기 좋아요</t>
+          <t>눈오는날 야외스톤스파는 정말 환상적이었어요~^^ 숙소도 레스트리는 깨끗하고 잘 관리되어 있었어요</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1592,11 +1592,11 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>뷰가 좋았어요 깨끗하고 잠도 편하게 푹 잤어요^^통유리창이 깨끗했음 하는 아쉬움이있었어요</t>
+          <t>시설이 너무 깨끗하고 직원분들도 친절하셨어요.스파도 종류가 다양해서 좋았어요 실내풀은 유아들이 놀기좋은거같아요~다음에 또 갈거예요</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1604,11 +1604,11 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>너무좋았습니다 곽지해변과 가깝고.직원분들 친절하고  청결했으며재방문의사있어요 ♡</t>
+          <t>너무좋아용!!! 근데 밥은 안에서 해결해야하는데 꽤비싸요 근처에 먹으러 갈곳이없어요 그래도 시설이나 그런건 좋아허요 애기들이랑 알차게잘놀이ㅡㅅ어용</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>룸상태 좋고 시스템 좋고 장소 좋고 단골이 되었습니다 룸상태 좋고 시스템 좋고 장소 좋고 단골이 되었습니다 룸상태 좋고 시스템 좋고 장소 좋고 단골이 되었습니다 룸상태 좋고 시스템 좋고 장소 좋고 단골이 되었습니다</t>
+          <t>여행가면 잠자리가 바뀌어 잠을 설치는 편인데 리솜은 침구류가 너무 편안해서인지 꿀잠잤어요!! 또 가고싶은 숙소입니다~</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1628,11 +1628,11 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>뷰가 좋았고근처에 식당도 많아서접근성도 좋았습니다.프론트 직원이 친절해서기분 좋았습니다</t>
+          <t>칫솔 치약을 제외한 비품들은 숙소 내에 마련이 되어 있었고, 초여름에 갔는데도 불구하고 벌레 방역이 잘 되어있었습니다.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>전망도 좋고 까끗하고 친절하시고 너무너무 다 만족스러워요!! 다만 넷플릭스가없어서 많이 아쉬웠습니다 ㅠㅠㅠ 침구 푹신하고 꿀잠잘수있어용</t>
+          <t>숙소 구경하면서 디자인 하나하나 다 신경 쓴 것 같아서 보는 눈이 너무 만족스러웠으며, 사람들이 다 친절해서 너무 좋았습니다!</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>인테리어도 너무 좋고 직원분들도 친절하고뷰맛집이네요 무엇보다 해변이 가까워서너무 좋았어요~</t>
+          <t>부모님 모시고 다녀왔는데 단풍시즌이라 너무 좋아하셨고 5개월 아기도 불편함 없이 잘 다녀왔습니다 친절끝판왕</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1664,11 +1664,11 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>좋았어요~~~ 오션뷰인네 2층이라 오션이 잘 보이진 않아요 그건 아쉽습니다 바다냄새도 나고 좋습니당 !!!</t>
+          <t>가족과 다시 찾은 리솜은 세월은 지났지만 여전히 매력적인 공간이였습니다. 가을이 오면 다시 찾을 예정입니다</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>화장실. 침대상태. 너무 깨끗하고,  내부 그림. 조명등도 좋았습니다. ~~^^ 위치도 좋고, 인근 고기국수집도 추천해 주셔서 맛있게 잘 먹고 갑니다. 다음에도 제주 가면  꼭  재 예약 . 방문 예정요~~^^</t>
+          <t>숙소는 너무 깔끔하고 좋아요시내와 접근성이 떨어지니 안에 해결해야 할게 많은데 식당과 스파이용료가 좀 비싼편이네요</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>프론데스크 직원분들 모두친절객실 컨디션 생각보다 좀 작은거빼곤 뷰 청소상태 모두 좋았음(전기 아울렛 상태 헐렁하던데 얘기한다는게 깜빡)앞에 과물치킨집있어서 매일 사다먹음 편의점도 바로앞에있어 매우 편리애기있는 사람들은 앞 해수욕장에서 놀기너무 편함다음에 애월가면 무조건 또 감</t>
+          <t>너무 잘 자고 왔습니다서울에서 딸이휴가나온 아들은 양구에서제천에서 만나 늦은 밤 10시에 들어가 아쉬웠습니다즐기고 싶은 숙소였는데</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -1700,11 +1700,11 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>뷰가 너무 좋았어요 근데 예약할때 룸 사진은 카펫이 아닌 그냥 마루바닥 같은거라서 아기랑 같이 묵을꺼라 일부러 방 바닥을 보고 골라서 여기로 예약한건데 막상 입실하고 보니 바닥이 카펫이어서 당황했네요 연박이었는데 중간에 청소해주실때 바닥은 청소를 안해주셨는지 빵가루가 그대로 였어요.. 날씨가 좋았다면 뷰가 너무 좋아서 그래도 괜찮았을텐데 하필 강풍주의보가 떨어져 바닷바람소리가 너무 커서 아이와 잠을 설치긴 했어요 아마 테라스 때문에 창이 1개 뿐이라 방음이 잘 안된거같아요 그런것만 빼면 카운터 직원분들도 친절했고 주차장도 괜찮았고 뷰도 괜찮았고 바로 앞에 편의점도 있고 괜찮았어요</t>
+          <t>숙소는 시간의 흔적이 많이보였지만, 주변 관경과 놀거리 모두 너무 좋았어요잘 쉬다 갑니다~</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>직원분들. 짱친절해요.2박꿀잠잤어요^^외관이 노후되긴했지만곽지해수욕장 코앞이고아침수영도하고 완벽했습니다~~!다음에도 올게용!!!!</t>
+          <t>매우 청결하고 깔끔한 숙소였어요.가족이나 연인과 함께하기 좋은곳이에요.스파시설도 좋았습니다.다시 방문하고 싶습니다.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>직원분들도 친절하시고 방도 깨끗해서 좋았습니다.전망은 사진에서 보던 것보다 더 좋았고요</t>
+          <t>1박 2일 가족들과 즐겁게 잘머물고 갑니다^^특히 나만 알고 싶은 마묵라운지 가격도 착하고 참 좋네요^^</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>곽지해수욕장 바로 앞이여서 뷰도 좋았고 산책길도 잘되있어서 좋았습니다. 침대도 더블로 두베드가 있어서 친구랑 편하게 잤고 매트리스도 너무 딱딱하거나 푹신하지 않아서 허리가 아프지 않았습니다. 방이 조금 좁은 편이긴 하지만 지내기에 불편한 정도는 아니였습니다. 위치도 애월과 가까워서 서쪽으로 여행코스를 계획하신다면 다니기도 좋을 것 같습니다. 주차장도 여유가 있었습니다!</t>
+          <t>첫날은 날씨가 흐렸지만 다음날 날씨가 너무 좋았어요 안에 산책로도 너무 잘되어 있고 스파까지 같이하니 힐링이네요. 직원분들도 친절하고 만족합니다 추천해요</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1748,11 +1748,11 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>곽지해수욕장 에서 가까워 잡았는데 비가 와서 파도도 높고 날이 흐려 못 놀아서 참아쉬운 숙소입니딘</t>
+          <t>산속 별장같은 분위기가 너무 좋았어요~공기 좋고 조용해서 정말 힐링 제대로 하고 왔어요♡</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>바갓가 앞이라 해수욕하고 오기 너무 좋앗고 숙소도 청결했습니다!직원분들 너무 친절하셧어요!</t>
+          <t>숲속에서 일어나니 새소리가 들리고 너무 기분좋았습니다.스파도 같이 했더니, 공기로 힐링하고 물로 힐링하고 컨디션 회복 제대로 하고 왔습니다.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1772,11 +1772,11 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>뷰 좋음.편의점 가까움.객실 깨끗함.직원분들 잘 웃어주심.수건 4개 있는데 추가시 금액 지불해야됨.수건 돈 받는 곳 첨 봄.그거 말고는 다 좋음.</t>
+          <t>스파랑 같이 이용했는데 좋았어요 다만 4명이서 이용해서 침대에는 2명이 자고 2명은 바닥에서 자야해요!!</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>곽지해수욕장이랑 가까워서 넘 좋았고 숙소 주변에 식당들도 있는데 맛이 괜찮았어요 주차도 편했습니다</t>
+          <t>쉼을 위한 정말 좋은 장소였습니다. 또 가고 싶은 깔끔함과 고즈넉한 그 곳. 빌라동 숙박 추천합니다~</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -1796,11 +1796,11 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>세안용 클렌져가 빠져있어서 아쉬웠네요.요즘은 거의다 그정도의 급에는 넥플릭스도 되고컴퓨터도 있고, 가장 기본으로 핸드폰 등의 충전기가 없어서 빌렸는데 훔쳐갈일도 없고 카드 제출하면서 체킹될껀데 보증금을 1개당 만원씩은 솔직히 불쾌했네요.그리고 숙소안에 음료도나 커피믹스ㆍ차티백도 없고.그냥 생수2개만 있는게 그냥그랬네요.오션뷰를 했는데 오션뷰는 커녕 동네 골목뷰였네요.</t>
+          <t>뷰모님이랑 동생이랑 잘 놀다왔어요! 욕실이 정말 좋았고 스파는 꼭 하시는 걸 추천드려요~~</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -1808,11 +1808,11 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>우선 사모님(?)이 웃으며 인사를 해주셔서 너무 기분이 좋았습니다. 객실이나, 상태는 일반적이였구요. 다만 아기 침대가드를 요청했었는데 없다고 하시더라구요, 대신 저렇게 침대를 붙여주셔서 아주 편안하게 아이와 잘 수 있었습니다. 다만, 에어컨을 통한 공기 난방이기 때문에 조금 건조할 수 있어요~</t>
+          <t>객실이 깨끗하고 쾌적했습니다. 아이들 데리고 한적한 곳에서 수영하고 노천당 즐기기 아주 좋았습니다.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -1820,11 +1820,11 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>복도에서 홍어 삭힌 냄새가 났고 방 안으로 들어와서 이에 대해 문의함. 페브리즈를 복도에 도배하는 것으로 해결. 신기하게도 머문 층의 복도에서만 그 불쾌한 냄새가 난 걸 확인해서 그렇게 화는 안 났음. 다만 프론트 직원분이 분명 코가 막힌게 아니라면 비록 방을 잠깐 사용했어도 바꿔줄 법 한데, 죄송하지만 곤란하다는 반응이 아니라 진작 말 안한 너희 잘못이고 이러면 청소를 다시 해야하는데 어떡하라는 태도로 불친절하게 답변한 건 서비스 미스임. 오전 타임의 여자 직원분은 반면 매우 친절해 보였음. 뷰는 좋긴 한데 방 위치에 따라 가려지는게 있음. 방에 어매니티는 정말 없다고 봐도 무방함. 굳이 애월에 있어야 하는 게 아니라면 제주 시내 널린 10만원 대  별 달린 호텔을 가는 게 맞음. 싸지도 않고, 모텔 수준임.</t>
+          <t>좋았어요잘때 외풍이있어서 바닥은 따듯한대 공기가 추워서 잘때 조금 불편했어요밤에 별이 잘보여서 좋았어요</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -1832,11 +1832,11 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>사진이 없긴 한데 그냥 호텔 느낌보단 조금 모텔~호텔 같구요 창문 쪽에 창틀? 이런데 먼지가 꽤 있어서 아쉬웠어요 그래도 가성비로 괜찮고 잘 때 방음 잘 되는 게 중요한데 방음은 좀 되는지 조용히 잘 잤어요 화장실 깨끗해서 좋아요 수압도 세고! 호텔 주차장에 전기차 충전하는 자리 없어서 아쉬웠고 호텔 주변에 전기차 충전할 곳이 몇 군데 있는데 거의다 이용하기 힘든 곳이라 좀 아쉬웠어요ㅠㅠ</t>
+          <t>객실이 너무 깨끗하고 넓어요! 나중에는 포레스트도 이용해보고싶네요~~ 둘레길 걸으면 별도 많이 보입니다 :)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>기대이상으로 좋았어요뷰도좋구 시설도 깔끔하고 좋았어요다음에 또 이용하고싶어요</t>
+          <t>경치도 이쁘고 산책로가 있어서 저녁에도 가벼운 산책하고 즐거운 여행했어요.다음에 또 여행가고 싶은곳 입니다.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -1856,11 +1856,11 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>아들 면회갔다가 묶었는데 추가비용을 받아서 조금 언짢음..객실이 비좁음.. 침구는 좋고 에이스매트도 좋았음</t>
+          <t>왜 다들 리솜 리솜 하는지 알게 되었습니다.돈 많이 벌어서 꼭 꼭 회원권 사러 가겠습니다!!!</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>약간... 처음에 문제가 있었으나해결해주시는 모습이 참 친절했습니다.스위트룸은 정말 30평 아파트 같았어요.이번에 신축아파트 입주하는데 저희 아파트보다 좋더라구요..거실에 소파에 티비도 크고 방마다 티비있고 온도도 방마다 조절되서 따뜻하게 잘 잤습니다.</t>
+          <t>창밖에 숲만 보이는 뷰가 너무 좋았어요 퇴실때 비 엄청왔는데도 밖 쳐다만봐도 힐링 이였습니다 ㅎㅎ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -1880,11 +1880,11 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>근처에 해수욕장을 제외하면 밥집이 많지 않아서 그건 고려하고 오셔야 할듯 합니다.  다만 가까이에 애월빵공장이 있어서 거기 방문의사가 있으시다면 1박을 해보는것도 좋을 듯 합니다^^</t>
+          <t>두번째 오는거였는데 포레스트는 처음이었어요호텔동보단 조금 노후됐지만 온돌방이 있어서아기 재우기 좋았습니다^^</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>곽지해수욕장 바로 앞이라 해수욕하는데 접근성이 좋아 매우 만족스러웠어요!숙소 위치가 해변이 바로 보이는 곳이라 바다가 보여 좋았고, 작은 테라스도 있어서 젖은 옷 말리는데도 용이했어요.침구, 티비 등등 시설이나 청결도는 매우 만족스러워서 하루 편하게 잘 지내다 갑니다!한가지 아쉬운 점은 늦은 퇴실 패키지로 예약했고 체크인때도 확인했는데 침실 청소해주시는 분께 전달이 되지 않았는지 퇴실 시간 전에 마스터키로 문을 열고 들어오셔서 매우 당황스러웠습니다ㅠㅠㅠ다음엔 이런 일이 생기지 않도록 잘 체크해주시면 좋을 것 같아요</t>
+          <t>두번째 오는거였는데 포레스트는 처음이었어요호텔동보단 조금 노후됐지만 온돌방이 있어서아기 재우기 좋았습니다^^</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>친절하시고 방 깨끗했어요~ 바닥이 카페트이긴 하지만,,,테라스에서 맥주라도 한잔할라고 일부러 테라스 있는방으로 골랐는데, 어쩐지 테라스 있는 방인데 왜 더 저렴하지 했더니, 1층과 2층이네요. 좀 더 잘 알아봤어야 했는데, 그래도 2층으로 신경써서 주시더라구요~날춥고 바람엄청 불어서 테라스도 못 써봤어요... 생각이 짧았어요....ㅜㅜ 그래도 겨울인데..ㅜㅜ지에스 편의점이 가까워요~애월까페거리에서 10분내외?배민켜보니 애월까페거리쪽에 있는 식당들이 배달범위더라구요~</t>
+          <t>작년 8월엔 사람이너무많았는데 이번엔 스파도 조용하고 너무잘놀고 쉬다갑니다 너무 좋은 숙소^^</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -1916,11 +1916,11 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>오전 오후에 계신 분은 매우 친절하셨는데새벽에 계신 분은 뭐 때문인지 굉장히 쌀쌀 맞으시더라고요시설이나 뷰는 좋았습니다바다뷰도 보이구요 ~</t>
+          <t>들어가는 입구부터 바깥과 분리되어 숲안에 위치한것이 좋았습니다. 숙소는 깨끗했습니다. 넓고 산책로가 많아서 산책하기 좋았습니다.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -1928,11 +1928,11 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>곽지해수욕장 인근에 위치해 있어 어린 자녀들이 놀기에 좋을 것 같아요.저희는 아이들이 커서 숙소인근에서 놀지 못하고 차로 이동해 놀고 오는 불편함이 있었네요</t>
+          <t>비가 와서 좀 아쉬웟지만 탁 트인 마운틴뷰가 좋았어요! 가족들이 다 만족스러워 했던 여행이었네요</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -1940,11 +1940,11 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>그래도 장점은 있습니다1.뷰가 아주 좋아요2.주차장이 넉넉합니다(지하도 있음)3.편의점 ,카페 1분거리 위치4.손 뻗으면 바다 산책 가능5.금연이라 그런지 방에서 담배냄새 안남6.여자사장님? 친절함7.자는 부분 깨끗함단점1.화장실 = 곰팡이 집2.카펫 먼지 천국(결국 알레르기 약 먹었어요)3.에어컨도(히터) 위와 마찬가지4.손님의 말을 귀담아 듣지 않음5.누수로 안한 벽 곳곳에 자국 6.하수구 냄새7.냉장고 의문의 머리카락8.라면. 탕. 회 등등 냄새나는 음식 불가(어차피 안먹을ㄹ거여서 상관없었지만 알고 오셔야 편하겠죠?)9.노래방 이용불가*음식. 노래방 공지 미리 앱에 등록해놓으세요 사장님 이 호텔이 깔끔하다고 하시는 분들은 집이 진짜 더러우신가 봐요.침대는 깨끗하죠 침대만요 ㅎㅎㅎ화장실 진짜 역대급이요샤워기 물 때랑 곰팡이가 있는데요.. 물줄기 나오는 곳에 곰팡이가 더덕더덕 껴있는 건 처음봐요!물트는 손잡이 + 세면대 (보이는 곳 만 깨끗) 커튼도 ㅋㅋㅋㅋ 곰팡이...보니까 아주머니가 하시던데 일주일에 한번씩이라도 락스 해달라고 하면 청소비 더 드리나요?왜 화장실 청소 검사를 안하세요?점검도 안하시고 그냥 아 했겠지~ 하시나요?저는요 리뷰를 안써요 좋으면 땡잡은거고 나쁘면 똥 밟았다공 생각합니다 （ •́ .̫ •̀ ）근데 이런 단점들 다 참을 수 있는데요...왜 제 방에 들어요셔서 물건을 건드세요? ㅋㅋㅋ룸청소 필요 없다고 분명히 전달드렸고 그때 직원3명이 같이 들었습니다 ㅋㅋㅋㅋ 한명도 청소 아줌마한테 전달을 안 하셨다고요?....청소는 청소인데요 왜 제 물건을 건드시냐고요저는 물건위치 정확하게 기억하거든요 정말 불쾌합니다저는 이 문제만 아니면 그냥 리뷰 안쓰고 가런갑다ㅏ 했을 거예요</t>
+          <t>또 가고 싶어요. 스파가 좋았고 관리가 잘되어있어서 깨끗했어요. 이외의 부대시설도 다 좋았어요.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>여사장님이 너무 친절하시고 업텐션이셔서 숙소에 대한 평가가 높아집니다. 근데 오션뷰로 예약하기엔 바다가 좀 거리가 있고 3층이라 잘 보이지도 않아서 가성비가 좀 떨어진다는 생각이 있네요. 바닷가라 약간 짠내가 호텔 자체에서 나긴하는데 객실 안에서는 안나서 좋았습니다. 객실 내부는 청결하고 만족한 숙소였습니다.</t>
+          <t>생각보다 사람이 많았지만 객실은 정말 깨끗하고 너무 좋았습니다~ 다음엔 여자친구랑 방문할게요~!!</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -1964,11 +1964,11 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>가족끼리 성인 4인이 묵었어서 더블침대 2개있는 일반룸했는데 사이즈가 뭘 시켜먹는다거나 뭘하긴 좀 작고, 어차피 제주관광을 위주로 하면 어차피 늦게 들어가기 때문에 딱 잠만 자기 괜찮은 것 같아요. 담에 가면 테라스 있는 방으로 해야겠어요 ㅎ.ㅎ 하지만 아침에 일어났을 때 보이는 뷰와 방의 청결도, 근처 편의점과 구경거리 등 편의성 생각하면 전체 평점결론은 좋다!! 입니당ㅎㅎ</t>
+          <t>깨끗한 시설에 직원분들 친절하시고 스파시설도 만족스러웠습니다 산책길도 잘되어있고 다음에 또 방문하고 싶습니다</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -1976,11 +1976,11 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>전반적으로 만족합니다바로 앞 상권과 해수욕장,지하주차장이 있어 편리합니다하지만 오션뷰 창문 앞 캠핑사이트가 있어 창문을 열고 있기 꺼려집니다</t>
+          <t>새롭게 지은 리조트라 시설이 훌륭합니다. 조식도 훌륭하구요. 가족들과 왔는데 불편함은 없었습니다.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5층객실 받았는데 일단뷰가 미쳤고...저녁에 펍에서 나오는 노래&amp;파도소리 테라스에 앉아서 힐링지대루 했습니다. 직원분도 친절하게 객실들어가전에 주의사항 말해주시고 다음에도 이호텔을 찾고싶을정도로 만족스러웠습니다.</t>
+          <t>너무 깔끔하고 만족스러웠어요 !직원분들 응대도 친절해서 좋았습니다다음엔 포레스트도 가보고 싶네요</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>곽지해수욕장 바로 앞에 위치하고 있어서 선택한 숙소입니다. 얼마전에 리모델링을 해서 시설이 깔끔합니다. 다만 객실 현관까지 카펫이 깔려있는 것과 샤워부스 턱이 낮아서 세면대쪽까지 물이 올라오는 것이 단점이었습니다. 그것만 제외하면 만족할만한 숙소였습니다. 직원분들도 아주 친절했어요 :)</t>
+          <t>레스트리는 조식이용도 편하고 헤브나인 스파 이용하기도 편해요~~ 언제나 와도 힐링되고 좋은곳이예요~~</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -2012,11 +2012,11 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>곽지해변을 바라볼수 있어 좋았습니다. 마지막날 아이가 해변에서 노는걸 좋아하여 체크인 11시에서 2만원 비용주고 2시간 연장을 하였습니다 혹시나 수건이 모자를까 요청을 드렸는데 안된다고 하시네요 비용을 내야한다고 3박을 여기서 다묵었는데 단천원이였지만 그거때문에 기분은 좋지않았습니다.</t>
+          <t>추운 겨울 스파도 즐기고 겨울 설경을 보고 싶어서 가족과 함께 방문했습니다~! 눈이 오길 바랐었는데 눈까지 내려서 더욱 멋진 풍경에서 놀 수 있었어요ㅎㅎ 생각보다 커서 이곳 저곳 돌아다니며 물놀이 할 수 있었어요객실은 포레스트G40 이용했는데, 깨끗하고 괜찮았지만 숙박비에 비해 좀 아쉬운 부분들이 있었어요 일단 바닥이 차가운 부분들이 많았고 숙소 들어가자마자 한기가 느껴졌어요 난방이 안틀어져있는 상태였어서 들어가자마자 난방 켜고 패딩입고 꽤 오래 있었는데 그래도 춥더라구요ㅠ 침대 없는 방은 온돌방이였는데 춥길래 요랑 이불 깔아놨더니 그 부분만 그나마 조금 따뜻해졌고.. 온도가 쭉쭉 높아져야하는데 너무 시원찮고 난방 이상 있는 거 같아서 프론트에 전화했는데 난방 관리 기사님(?) 불러주셨는데도 추위가 비슷해서 다시 전화드렸고 방 바꿔주셨어요 똑같은 G40방을 배정 받았는데 난방은 미리 틀어두셨어서 이전과 달리 한기는 덜 느껴졌었어요 그래도 바닥은 부분부분 차더라구요ㅠ 난방이 잘 안돼서 이전 숙소에서 패딩입고 있고 닭강정 시킨 것도 프론트 통화하고 기사님 방문하고 방 옮기느라 제대로 못먹고 시간 버렸는데 룸업그레이드도 없고 바닥 찬기는 거의 비슷했어서 아쉬웠네요ㅠ 룸컨디션 괜찮은지 여쭤보셨는데 시간도 늦었고 또 바꿔도 비슷할 거 같아서 그냥 거기서 묵었어요 그래도 12시 체크아웃으로 늘려주셨던 점은 좋았어요 바꾼방 침대있는 안방은 따뜻했고, 온돌방은 따뜻해져서 뜨끈하게 잤고 화장실은 추웠고, 거실은 바닥이 차서 약간의 한기가 느껴졌어요 그래도 직원분들 응대가 좋았고, 스파와 뷰가 넘 좋았어서 언젠가 한 번쯤 또 갈 지도?! 대신 다음에 오게되면 겨울에는 안 갈 것 같고 신축 건물인 레스트리에 갈 거 같아요</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -2024,11 +2024,11 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>직원분들도 친절하시고 대부분 좋았는데 방음이 전혀 안되는지 일요일아침7시부터 옆방 애기가 자지러지게 우는 소리에 깼어요 하아 ㅠㅠ 푹쉬러온건데 4시간자고 나왔네요...</t>
+          <t>다들 왜 리솜리솜하는지 알겠더라구요가족들이랑 1박 2일으로 다녀왔어요할머니도 모시고 갔는데 하루 더 묵고싶다고 하시더라구요 🥲그 만큼 너무 만족스러웠습니다 다만 부대시설을 이용하려면 카트를 이용해서 왔다갔다 해야하는데 젊은 분들은 무관하지만 연세 있으신분들이 왔다갔다하려면 힘들더라구요 ㅠ무료 제공은 체크인 체크아웃 +1회 밖에 제공이 안되고 추가로 요금 지불 해야하는게 많이 아쉬웠어요일식집 저녁에 회랑 나베도 너무 맛있었고 다만 너무 오픈된 장소라 말소리가 다 들리는 건 좀 아쉬웠어요가격도 좀 있는 만큼 서비스를 더 높이면 어떨까 싶어요!마지막으로 스파 정말 좋았어요 사진 찍기도 좋고 눈이 즐거웠네요 :)참고로 어메니티는 샴푸 린스 바디워시는 있으나 치약칫솔 없으니 챙겨가세요 !! 다음에 또 묵고싶어요!! 친구들이나 커플끼리 가도 좋을 것 같아요 😍</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>문을 열고 들어가서 첫느낌은..첫눈에 반함.ㅎㅎ곽지해변의 푸른바다와,  세련되고 깔끔한 방컨디션에도 이호텔의 선택은 정말..잘했다는거.^^주변에 맛집이 있어서 더더욱 즐겁게 보내고 왔습니다.감사합니다.</t>
+          <t>조용한 숲속 휴식 정취를 느끼기엔 좋은곳. 헤브나인 스파시설도좋고 투숙객 50% 할인. 휴일이라 나이트 스파 좋았음. 리조트 내 일반차량 이동 못하고 운영중인 카트 이용. 체크인/아웃 카트 2회 기본 제공. 추가 카트 이용권 3장 받음. 레스트리는 호텔 건물. 포레스트 빌리지는 독채. 조식은 레스트리 건물 지하1층.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -2048,11 +2048,11 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>위생, 청결 부분에서 최악이여도 괜찮으신 분들 가셔요..여기저기 찍는것도 거북해서 커텐에 있는 얼룩 딱 한 부분 찍었는데... 여기말고도 굉장히 얼룩들 많구요..화장실은 곰팡이 천국이고 수건에도 먼지투성이여서 씻고 나와서 닦으면 먼지들이 몸에 붙어있구요..하하</t>
+          <t>😸 숙소 깔끔하고 비록 위치는 차 없이 갈 수 없는 고립된 산 속이지만 안에 놀거리(스파수영장, 오락실 등)&amp;먹을거리 다양해서 좋았습니다! 😸 산책길도 잘 마련되어 있고 그 사이로 폭포물이 작게 흘러서 소리도 너무 좋더라고요! 날씨 괜찮다면 꼭 걸어보시길 추천드려요😸 스파 패키지로 스파까지 이용했는데 넓고 풀도 다양하고 아주 재밌게 놀았습니다! 돌도 안된 아기들부터 어린이들까지 어린 아이들이 많았는데, 키즈풀도 따로 있는 만큼 아이들도 놀기에 좋아보입니다😿 모든 이용시설과 건물이 일찍 마감하고 불이 꺼집니다. 밤에는 정말 아무것도 할 게 없고, 심지어 산책하려고 나왔는데 산책길 주변에 정말 컴컴했고, 레스트리에서 포레스트로 걸어갔는데 그 입구부터 불이 다 꺼져있더라고요. 저희 가족처럼 밤에 활발해지시는 분들은 좀 더 고려해보셔야 할 것 같습니다!</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -2060,11 +2060,11 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>나쁘지 않아요 친절해요칫솔같은 어메니티 다 있어요 긍데 넷플릭스나 티비 다시보기 기능도 없웃우요 제일 작은 방이긴 했어용 침대가 좀 딱딱 햇어요 오히려 좋은 분도 계실지도?</t>
+          <t>스파와 가까워서 호텔을 선택했어요다 좋았는데 4인실 원룸형이라는건 알았지만 작아도 넘 작아요 싱글 2개에 이불 2채인데 이불을 다 펼 자리가 없어요 다른 호텔 2인실과 같아요야외 너무 추워서 스파는 밥먹는시간 포함 2시간만에 나왔어요 봄이니 가을에 와보고싶어요</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -2072,11 +2072,11 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>호텔은 깔끔하고 좋았는데 호텔에도 그주변에도 갈만한데가 별로없고 오션뷰이긴한데 그사이에 주차장이 길게있어서 딱히 오션뷰의 느낌도 별로 없었던것같아 아쉬웠어요. 진짜 딱 잠만자는 호탤로 작당한것 같아요</t>
+          <t>국내 여행가본 숙소중에 최고였습니다.스파, 조식 나무랄게 없었습니다.가족들과 소중한 추억 만들었습니다..</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -2084,11 +2084,11 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>화장실만  최고  그래서 별1개...  객실의  메트리스와  천장은 최악의 숙소였어요ㅜ.. 더블침대 2개여서 좋아했는데,  침대 메트리스는 꺼지고, 누우니 등쪽은 배겨서  잠을 자기 힘들었어요..불을 켜고  천장을 보니, 호텔  천장이  노출  컨셉인가봐요.. 콘크리트인지  합판인지  사진과 같은 천장 마감이었어요.. 많은 숙소를 다녀본것은 아니지만, 이런 메트리스와 천장마감은 경험해본적 없었네요...밤에 직원분에게  메트리스에 대한  불만을 제기했지만,    빈방도 없고,  메트리스  큰 문제는 없어 보인다,  그저 미안하다,  호텔 후기도  좋으며  메트리스 불만제기한  손님없었다,  가장 저렴한방이다 (8만원대)라고   대처하심..꺼짐이 덜하고, 등이 덜 배긴  가장자리에서 밤새  겨우  잠을 청하고  퇴실할때  로비에서  직원을 찾았지만,  로비엔  아무도 없었음....두번 다시 찾고 싶지 않은  숙소였음 ㅜ...</t>
+          <t>숙소는 상태 좋은데..우풍이 쎄네요.ㅎㅎ바닥 보일러는 뜨끈한데 우풍이 쎄서..애들이 기침을 해요~ 숙소들이 거리가 있어서 많은사람들이 카트를 이용하는데..무료이용권 다 쓰면 금액내고 타야해요.ㅜ그게 불편하더라구요..안에 식다들은 진짜 비쌉니다~ㅎ..ㅎ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -2096,11 +2096,11 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>주차 하나는 쉽고 방음 잘되는 편같아요. 생각한것보다 너무 모텔 느낌이었어요. 콘센트도 침대에서 멀리있구요. 오션뷰라지만 바다가 조금 멀리 있는 오션뷰고, 프론트와 같은 건물이 아닌 옆동으로 무거운 캐리어를 옮겨가야했습니다. 이점은 좀 번거로웠어요. 아침에 체크아웃 해주신 여자 사장님?은 엄청 친절하셨어요!</t>
+          <t>부산에서 출발해 오후4시반에 체크인.12시부터 대기표받아 선착순 룸배정이라네요모르고 갔더니 뷰는 포기!뒷산배경인데  눈까지 내려 그나마 ...룸깨끗.성인자녀들 트윈침대에 만족.연박하고 싶다고~4시반에 헤브나인스파 입장5시반부터 눈이 내리기 시작~퇴장 5분전 눈이 절정으로 내리고 뜨거운 스파물거품에 좋은 추억 간직하고 돌아갑니다</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -2108,11 +2108,11 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>아..오션뷰라고해서 ..  ㅋㅋ잡았는데 하...네. 오션 ..뷰...입니다.그리고청결하진않습니다.</t>
+          <t>숙소 좋앗어요^^ 봄 가을에 가면 더 좋을거같긴해요부모님 모시고 좋은 여행이엇습니당</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -2120,11 +2120,11 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>입실 후 에어컨을 가동하였는데 더웠습니다. 전화로 문의 드렸더니 30분정도 더 있으면 시원해질거라고 말씀해주셔서 기다렸습니다. 그러나 시원해지지 않아 다시 전화드리니 나이든 남자직원분께서 방문해주셨습니다. 그러나 문제가 없다며 커튼치고 햇빛이 없는 저녁이 되면 시원해질거라 하셨습니다. 애초에 오션뷰를 예약했는데 왜 커튼을 쳐야하는지도 의문이지만 더위가 우선이라 커튼을 치고 생활했습니다. 에어컨을 가동한채로 밖에서 저녁식사를 하고 돌아왔는데도 더웠습니다. 다시 문의드리니 선풍기를 가져다드리겠다고 하셔서 알겠다고 했습니다. 젊은 남자 직원분께서 친절히 에어컨 상태도 봐주시더니 에어컨 필터도 세척해서 다시 주셨습니다. 추후는 시원해졌지만 사장님의 태도에 실망스러웠습니다. 덥다는 문의를 많이 받으신다고 했는데 그럼 대책이 필요할 것 같습니다. 남자사장님께서 젊은 직원분께 일을 떠맡기는 것 같고 회피하시는 것 같아 다소 별로였습니다. 쾌적하고 좋은 서비스를 바라시는분껜 비추천 입니다.</t>
+          <t>부모님 칠순으로 다녀왔는데 아주 쾌적하고 좋았습니다. 한가지 단점은 저녁 조식 식사시 대기가 길어 좀 힘든 부분은 조금 아쉽네요</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -2132,11 +2132,11 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>방도 사진대비 엄청좁고 자는데 알수없는 소리 (냉장고 전기흐르는잡소리) 그리고 방컨디션이 최악수준 곰팡이냄새도 많이납니다.. 사진만보고 평타수준이라도 기대했는데 이런방이무슨 10만원을받나요 ㅎㅎㅎ</t>
+          <t>포레스트 G70 1박후 레스트리 G70 1박하였네요.주변시설 이용은 확실히 레스트리  추천하구요.층간소음이나 프라이빗은 포레스트 추천합니다.주차장은 거의 비슷한데요.주말가면 주차장에 주차하기 빡세네요.헤브나인 스파는 주말이든 주중이든 일찍 가시구요.몬도키친 석식 뷔페는 대박이었네요.가성비 아주 좋았습니다.가재나 대게,킹그랩은 안나오지만 서울 웬만한 디네뷔페랑 비교해도 좋았습니다.몬도키친 조식도 무난했습니다.층간 소음이나 엘리베이터 이용 및 주차장 이용은 좀 불편했네요.주말 헤브나인스파는 좀 고려대상입니다.2월에 갔는데도 너무 많아요.불편함도 있고 좋은점도 있는 레스트리 G70후기입니다.참. 포레스트 G70은  냉동고있는 약간 큰 냉장고인데레스트리 G70냉장고는 냉동고 없는 작은 냉장고이므로 얼음 필요하시면 레스트리는 빠르게 소비하셔야 하네요.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -2144,11 +2144,11 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>부모님 대신 예약해드렸는데화장실 수압이 너무 약했다고 하네요변기수압이 약해서 물 두번 이상 내렸고 욕조에서 샤워후에 물이 안내려가서 찝찝했다고 합니다양치하는데도 양치 물도 잘 안내려가고..재방문의사 없어요..</t>
+          <t>예약이 너무 어렵다는 리솜포레스트 드디어 다녀왔습니다!풍경이 너무 예뻐요… 다만 객실 수압이 너무 약하고 온수가 안 나왔었어요🥹 그점 빼고는 모두 완벽했습니다 잘 묵고가요</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -2156,11 +2156,11 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>숙소도 깨끗하고 뷰도 좋고 직원분들도 친절하시고 좋아요</t>
+          <t>다 좋았는데요.제가 간 날 눈바람이 많이 불었는데요.샤시에서 휘파람 소리가 너무 심하게 나서 잠을 이루기 어려웠습니다. 서비스는 좋았는데, 바람 많이 불때를 대비해서 샤시 결착 보강이 필요할 것 같아요.나머진 다 좋았어요.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -2168,11 +2168,11 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>냉장고가 크고 뷰가 너무 좋았네요~</t>
+          <t>2층이라 계단이 많았는데 카트직원분이  큰캐리어도 안들어다주시고, 방바닥장판도 지저분했어요</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>전망좋고 깨끗한 숙소입니다</t>
+          <t>저렴한 가격에 휴가기간에 딱 방이 있어서 스파 패키지로 예약하고 갔어요. 처음이라 사실 하루만으로 충분할거라 생각했는데 실수였네요… 수영하고 다음날 오전에 산책 잠깐 하고. 너무 짧았어요 ㅠㅠ 다음에는 꼭 2박은 해서 하루는 푹 쉬는 날로 하면 좋을 것 같아요!정말 좋았어요!</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>접근성 괜창ㅎ고 바로 앞에 바다라 뷰가 괜탆아ㅛ어요</t>
+          <t>엄마환갑파티로 여행갔는데 숙소는 너무 마음에들었고 잘지내고왔어요ㅎㅎ 근데 리조트내 식당은 그 값어치를 잘못하는거같아요</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2204,11 +2204,11 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>깨끗하고 뷰좋고 친절하고 가성비도 좋아요</t>
+          <t>숙박은 레스트리 이용했고요스파여행 목적으로 간거였는데..너무 물이 찼어요ㅠ한파여서 그런걸수도 있는데 실내로 바람이 휭휭 들어와서 가운입고 실내 돌아다니기도 추운정도였어요실외는 아에 나가지도 않았네요감기걸릴까 걱정되더라고요실내바데풀도 진짜 들어갈때 서늘할정도..그안에있는 작은 온천탕?도 추워서 그런지 물이 36도..37도 정도~ 중간에 온도재고 가더니 좀 올라가더라구요키즈풀은 그나마 안쪽이라 좀 낫고요아기들 이용하기 좋을것 같아요 유치원이하~숙소는 괜찮았습니다직원들도 친절했구요12시 도착해서 미리 방배정받고 스파이용했어요저녁은 들밥애 이용했는데 반찬 많고 푸짐했어요3명이 2인시켜도 다 못먹겠어요조식은 가격대비 그냥 그랬습니다그리고 방에는 무료 생수2병외에 차같은건 없더라고요가격이 싼편은 아닌데어매니티도 비누랑 샴푸등 기본외엔 없어요식기류 포트 전자렌지는 비치되어있어요그리고 퇴실전 퇴실시간 알려주는 방송이 나오더라구요ㅎ별똥카페는 낮에 가봤는데 버기타고 가야되서 버기는 편도 5천원씩 입니다레스트리 투숙객도 버기 이용권이 좀 있음 좋겠네요겨울보단 가을에 이용하면 좋을것 같아요</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2216,11 +2216,11 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>만족합니다 만족합니다</t>
+          <t>포레스트 숙소주변 숲이 너무 좋습니다. 외부 식당등 이용이 좀 멀어서 미리 포장해오는것도 방법입니다.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2228,11 +2228,11 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>만족합니다 만족합니다</t>
+          <t>방 컨디션이나 시설은 정말 좋았어요근데 조식먹을때 직원 응대는 최악이였어요자리 안내해주는 외국인 남자분은 정말정말 친절하셨는데한국인 젊은여자분은 여태 받아본 서비스 중 최악이라 별 하나 뺍니다</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2240,11 +2240,11 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>객실청소상태  전반적으로깨끗함  조식서비스도운영했으면함</t>
+          <t>눅눅한 장농이 있는, 모기 많은 산속에 있는 리조트.야놀자 회원이라 그런 방을 준진 모르겠지만 24년 여름 휴가 최악의 경험을 했네요..비가 많이 와서 그런거겠지만 직원들이 힘들어 청소끝내고 문앞에서 담배를 펴서 자욱 한 담배 연기속에서 한바탕 하고 옴.야놀자 대행 업체이면 숙소 관리도 똑바로 하세요! 너무 열받아서 작성합니다.. 숙소에도 컴플레인 걸었습니다 수고하세요</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>화장실도 깨끗하고 침대도 편하고 만족했어요</t>
+          <t>한주내내 비가 와서 취소해야되나 백번고민하다가 떠난 가족여행이었습니다. 날씨도 도와줘서 비도 오지않고 편하게 식사하고 스파이용과 산책로까지 모두 만족했습니다.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>편하고 잘쉬고 갑니다</t>
+          <t>5세 둥이들과 다녀왔어요. 숙소뷰 최고였고 음식점도 너무 좋았고 직원분들도 친절했고 모든게 다 만족스러웠던 여행이었어요. 예약하기 힘든곳이라 급 예약해서 다녀온건데 다 너무 좋았던 여행이었습니다</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2276,11 +2276,11 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>침대도 편하고 주차하기 짱짱 편해요온돌이라 건조하지도 않고 직원들 친절하십니다</t>
+          <t>시설적이 부분에서는 딱히 흠잡을게 없었고 가격대가 좀 있지만 퀄리티가 괜찮은 편이라 so so인데 유독 스파 직원들이 불친절함 표정도 그렇고 말투나 톤이 뭔가 하기 싫다는 듯한 느낌을 받음</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2288,11 +2288,11 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>전망이 진짜 너무 좋고 숙소도 넓어서 너무 좋았습니다!</t>
+          <t>1월 초등아이랑 다녀왔어요솔직히 스파는 가격 대비 실망입니다가격대비 놀것이 없고아주 잘찍어야 리뷰에 나오던 사진 샷 나옵니다 ㅠㅠ스파하면서 간식 먹는곳은 정말 물 더럽습니다ㅜㅜ비위생적입니다 ㅜㅜ탕에도 찌꺼기가 둥둥가격대비 너무 별로예요저는비성수기 주중에 방문했음에도 별로였습니다레스트리타워 숙박했는데 난방이너무높아 더웠어요 전원을 꺼도 안내려갑니다데스크문의했더니 에어컨 리모컨 주는거 외다른방 교체 안되었습니다음식값 비쌉니다주변에 뭐가 없다보니 어쩔수없이 먹었습니다맛은 중간정도 합니다직원분들 친절합니다생글생글 웃는 얼굴은 아니고 지친 얼굴로 친절합니다다들 일이 힘드신가봅니다</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>사장님 친절하시고 위치 접근성 너무 좋아요!</t>
+          <t>벌레가많은건 어쩔수없지만, 프런트있는 동과 숙소동이 너무너무 멀어요 포레스트보다 레스트리를 추천, 안에서 밥먹는것도 너무 비쌈 ㅋㅋㅋ수영장은 좋은데 비치체어가 유료</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>편하게ㅣ잘 쉬었다 가요.</t>
+          <t>깨끗하고 넓고 편안한 휴식공간이었어요..헤브나인스파는 아주 따뜻하고 다양하며 시설이 잘 작동하고있었어요..인피니티풀은 자연을 바라보며 힐링하기 아주 좋은 최고의 겨울수영장이었네요.. 또 가려구요..</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>나쁘지않았습니다. 뷰가좋아요</t>
+          <t>다른건 다 좋았는데 예매할때 조식패키지로 분명 한거같았는데스파패키지로 되어서 돈 추가된게 아쉽네요ㅜㅜ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>예전에방문하고좋아서다시방문했어요역시나뷰가너무좋네요</t>
+          <t>44개월 아기와 함께 갔는데 애기랑 수영하기도 편하고 조식도 너무 잘나와서 좋었어요. 침대도 너무 편하네요.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>직원들이 친절했고 곽지해수욕장 뷰가 참 좋았어요.</t>
+          <t>예전부터 가보고 싶었던 곳인데, 드디어 다녀왔네요- 기대했던대로 모든 것이 만족스러웠어요-! 다만, 늦은 체크인으로 뷰가 좋은 방은 이미 다 나갔더라는.. ㅠㅠ 다들 체크인 미리하셔서 만족도를 더더욱 끌어올리시길..!</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2360,11 +2360,11 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>방이좋아요방이좋아요</t>
+          <t>깔끔하고 친절한 곳.전망도 좋고, 스파도 이용했는데 좋았어요(사람이 많긴해요)부모님 모시고갔는데 좋아하셨어요.엘레베이터가 4대인데 사람이 너무많아서 매번 탈때마다 너무 오래 기다려서 탄거 말고는 불편한거 없었어요!</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>친절하시고 방도 욕실도 넓고 좋습니다. 두번째 이용했는데 매번 만족했습니다 ^^</t>
+          <t>직원분들 친절하시고 서비스가 좋아요! 숙소도 넓고 깨끗해서 잠도 편하게 잤습니다. 해브나인 스파 이용했는데 샤워하는 동안 누가 수영복을 훔쳐가서 잃어버렸습니다. 여행가시는분들 조심하세요!</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -2384,11 +2384,11 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>숙소 깨끗하고 좋아요무엇보다 뷰가 좋아요</t>
+          <t>일-월 갔는데도 사람이 엄청 많았어요!숙소는 포근한 느낌이라 잠이 엄청 잘 왔어용손님 수에 비해 주차장, 엘리베이터가 부족해요체크인 체크아웃 시간에 엘베 한 10분 넘게 기다린듯 ㅠ주차장도 자리 별로 없고 간격 좁아요쇼파에서 꼬랑내 나요 ㅠㅠ가격이 싼것도 아닌데 쓰레기, 음쓰 내가 직접 분리수거하고 와야댐 다음에 간다면 그냥 숙박 안하고 헤브나인스파만 당일로 하고 올 것 같아용</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>굿굿 좋습니다 ㅎㅎ</t>
+          <t>진입로 벚꽃길 반길 때 방문했습니다. 산책따라 별똥카페  방문, 해브나인 스파, 조식 부패 등 전반적으로 좋았습니다.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>너무좋았습니다 굿굿</t>
+          <t>가족끼리 갔는데 너무 쾌적하고 만족하게 놀다왔습니다.다만... 냉장고가 모텔 냉장고라 음식 보관이 어려웠어요. 그리고 룸클리닝 서비스가 유료라서 의외였네요 ㅎㅎㅎ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -2420,11 +2420,11 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>전반적으로 만족했습니다</t>
+          <t>가족끼리 갔는데 너무 쾌적하고 만족하게 놀다왔습니다.다만... 냉장고가 모텔 냉장고라 음식 보관이 어려웠어요. 그리고 룸클리닝 서비스가 유료라서 의외였네요 ㅎㅎㅎ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -2432,11 +2432,11 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>큰 기대없이 급히 예약했는데...숙소보고 놀랬어요...잘쉬었습니다... ^^</t>
+          <t>포레스트숙소 문열자마자 어디서나는지 모를 지린내? 빼고는 조식도 산책길도 다 좋았습니다</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>큰 기대없이 급히 예약했는데...숙소보고 놀랬어요...잘쉬었습니다... ^^</t>
+          <t>더운 날씨라서 포레스트리솜은 이동하기 힘들었어요.날씨가 시원하면 가기 더 좋을것 같습니다.그래도 자연경관이 너무 좋았어요</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -2456,11 +2456,11 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>큰 기대없이 급히 예약했는데...숙소보고 놀랬어요...잘쉬었습니다... ^^</t>
+          <t>이불, 화장실 변기에 머리카락.금요일포함 평일은 야간온천 안되는점. 하지만 금요일 요금은 주말처럼 받는단 점. 부대시설 죄다 예약안되가지고 결국 청주까지 가서 먹고온 점. 온천 물 너무 미지근했던 점. 비싸긴 더럽게 비싼데 뷰는 너무 극단적으로 쓰레기였던점. 막상 온천은 온천수도 아니었던 점.이 돈주고는 다신 안갈것같습니다. 싸게가면모를까</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -2468,11 +2468,11 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>경치가 너무좋았어요!객실이 좀 좁긴했지만 저렴한가격에 깨끗하고 어차피 잠만 잘꺼니깐요!</t>
+          <t>우선 친절하게 맞아주셔서 감사합니다..생각보다 작아서 놀랬다는.. 화장실이 진짜 끝내줍니다~한번 놀러 갔다오기 좋은 곳</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>바다가 한눈에보이는 객실과 방컨디션도 좋습니다</t>
+          <t>청량함 속에 편안함. 제대로 힐링이 되요. 침구 모두 정갈. 제공 안 되는 칫솔 치약 챙기는것만 잊지 마세요~숲소리</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -2492,11 +2492,11 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>가격대비 너무 만족하고 사장님께서 친절하셔서 너무 좋았습니다.</t>
+          <t>전에 갔었을때 너무 좋았어서 이번에 재방문했어요저번엔 빌라였고 이번엔 레스트리에서 묵었는데 빌라쪽 직원분들이 더 친절합니다. 깔끔하고 쾌적하고 좋아요관리가 정말 잘 되어있습니다.</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>해변이 너무 좋아요~ 전망 굿~</t>
+          <t>호탤 깔끔하고 좋았어요 근데 화장실 환풍기를 트니까 먼지가 후두둑 떨어지더라고요.. 광장히 찝찝했어요 그 거만 빼면 다 좋았어요~</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>부모님 예약해드렸는데 정말 편하게 잘쉬다 오시네여 다음에도 꼭 재방문의사있습니다</t>
+          <t>레스트리 G40 룸컨디션 최고~직원분들 모두친절하고,헤브나인스파 및 부대시설 가족여행으로만족합니다.다만 전체적으로 가격대가 높은건 감안하셔야될듯,,^^;</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -2528,11 +2528,11 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>깔끔하고 어메니티가 아주 잘 갖춰져있었어요</t>
+          <t>숙소는 그냥저냥 괜찮았어요 스파는 확실히 겨울이라 춥긴했구요 근데 주변시설이 아무것도 없어서 먹을 식당도 할것도 없어서 숙소에만 있으실꺼면 상관없을것같지만  주변시설이용하실거면 다른지역이 좋을것같아요</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -2540,11 +2540,11 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>너무너무 좋습니딘ㅎㅎ</t>
+          <t>친구들과 여행으로 간 리솜. 예약이 힘들어서 시설에 대한 기대를 많이 하고 갔는데 레스트리g40 깨끗해서 만족합니다만 생각보다 거실이 좁아서 이쉬웠어요. 부대시설은 잘 되오 있어서 편하게 먹고 놀다 왔습니다</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -2552,11 +2552,11 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>숙소 뷰도 너무 좋았어요</t>
+          <t>배정받은 방 바닥이 깨끗하지 않아 얘기했더니 바로 치워줬습니다... 숙소에서 보는 풍경이 너무 좋아 힐링하고 왔어요~</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>깨끗하고 조용해서 좋았습니다.</t>
+          <t>스파도 같이 이용했는데 방문당시 인피니티풀이 점검중이라 너무 아쉬웠어요 ... 그래도 직원분들 다 친절하시고 자연속에 있어서 힐링여행 지대로 하고 왔어요!!</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -2576,11 +2576,11 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>뷰가 아주 끝당납니다</t>
+          <t>소문 보다는 실망이요스파만 하러가는 사람도 있다는데 그정도는 아닌것 같아요가족이 놀러가서 편하게 쉬기는 딱 좋습니다스파에 대한 큰 기대를 줄인다면 최고의 숙소 입니다독채는 카트 이용이 좀 많이 불편했어요일단 쉬는 공간으로는 좋아요</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -2588,11 +2588,11 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>주변에 볼건 별로없지만 바다만 보는건 강추해요!</t>
+          <t>진심 솔직 후기. 숲속이라 산책하며 힐링하기엔 괜찮지만, 딱 거기까지. 레스트리가 오히려 본관 편의시설과 가까워서 좋고 포레스트는 전부 빌라동이라 편의시설 엄청 멀고 돈 내고 카트 타고 다녀야함. 룸은 매우 청결하고 좋음. 주변에 뭐가 없기 때문에 리조트에서 맘놓고 가격 비쌈ㅎ 교촌 오리지널이 2만7천원임ㅎ 일반 식당도 2인기준 5만원 쉽게 넘어감. 수영장은 무조건 유료인데 인터넷이 더 저렴하나..솔직히 내가 너무 괜찮은데 많이 다녀봐서 그런지. 가격 3만6천원 돈 진심 아까움. 애들 노느라 어쩔수 없지만 애들 놀이 시설도 없음. 사진에 보이는 딱 그게 끝. 찜질방은 안가봐서 모르겠음. 조식도 그저그런데 4만원대임. 조식 패키지로 샀는데 조식 가격빼니까 딱 룸온리 가격 나옴. 할인이라곤 일절 없음. G40룸 자체는 매우 훌륭한데..진심 그게 다 임. 그냥 나 숲으로 놀러왔다고 거기에 만족할 수 있다면 좋음. 어린 아이들 데리고는 음, 글쎄..음. 멀리는 못 돌아다님.</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>날이 흐렸는데도 뷰가 정말 미쳤습니다 제주 첫 일정에 싸고 좋은곳에 묵게되서 행운이었어요</t>
+          <t>깔끔하고 접근성도 좋아 괜찮았습니다만 스파 온천물이 생각보다 따뜻하지 않았네요.. 좀 더 물 온도가 높았으면 좋겠네요</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>오션뷰에 객실도 저렴한편이며 깔끔해서 좋아용</t>
+          <t>방배정 체크인은 12시부터 가능하고 입실은 3시부터 돼요 스파도 좋았는데 애들이 많아서 그런가 물이..좀 더러워요ㅜ 이물질 둥둥 떠다니는게 눈에 보이고 애기들 그냥 침 뱉는거도 여러번 보고.. 스톤스파는 이용 가능 시간이 짧았지만 사진용으로는 나쁘지 않았고 오히려 아주 뜨거운 노천탕같은 탕에 앉아있는게 제일 좋았어요 숙소는 깔끔하고 넘 좋았어요</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>깔끔하고 죠습니당~~</t>
+          <t>부모님이랑 온천 즐기기 좋았어요~ 호텔은 역시 깨끗했어요!! 숲속 힐링하는 기분이였지만 프론트에서... 모르는거 물어보는데 컴퓨터 보면서 답해서 살짝 기분 안좋았습니다</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>주차장넓고 방도넓고 비록비가왔지만 바닷가도바로보여서좋았어요!</t>
+          <t>2박갈껄 엄청 후회했습니다.들풀애에서 메뉴주문시 식사가격이 비싸다고생각했는데, 반찬이 엄청나와서 좋습니다.</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -2648,11 +2648,11 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>가족끼리가기나쁘지않음</t>
+          <t>숙소는 좋으나 직원들 응대나 서비스는 만족스럽지 못하네요. 지금까지 이용했던 호텔들은 물 정도는 정수기나 추가 배급이 되던데 여긴 일절 없네요.풍경은 좋았습니다. 산책로 등은 매우 만족해요.</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>곽지해수욕장 바로 앞이고 숙소도 괜찮아요</t>
+          <t>리셉션직원이 매우 친절하고, 전망이 넘 예쁘게 잘 꾸며서 잘 쉬다 갑니다. 다만, 주차가 매우 불편하고, 전체적으로 드라이브하긴 부적합한점이 아쉽습니다. 또한, 트윈룸과 연결된 욕실에서 코를 찌를듯한 하수구냄새로 사용이 어려웠습니다.</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -2672,11 +2672,11 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>괜찮습니다.직원분들도 친절하세요</t>
+          <t>1. 친절 및 서비스는 좋지도 나쁘지도 않았음. 오후2시경 도착했는데 포레스트동 200실? 중에 약 120실이 이미 체크인 예약 완료 된 상태ㅡㅡ 원하는 위치로 배정받고 싶으면 도대체 몇시에 가서 줄을 서야 하는가?2. 청결도는.. 포레스트동은 조금 오래된 리조트 느낌이었음. 구조적 특성상 호텔보다 청소하기 어렵다는 걸 감안해도 구석구석에 먼지가 보였음. 3. 해브나인스파에 대한 기대가 컸는데 별로 였음. 패키지로 갔으니 이만하지, 제 돈 다 주고 간거였으면.. ㅎㅎ 사우나 내에서도 탈의실과 욕탕 내부 구조도 너무 동선이 길어서 불편하고.. 일부 사람들은 핸드폰을 방수팩에 넣은 채 사우나 내부를 돌아다니는데 저게 켜져있는건지 꺼진건지 매우 찝찝함. 핸드폰 작동 여부를 떠나서 탕안에는 아예 못들고 들어오게 했으면 좋겠음.4. 위치는 제천 시내까지 차로 20~30분 거리였음.아침에 일어나서 듣는 새 지저귀는 소리는 매우 평화로웠으나, 전반적으로 지불한 금액 대비 만족도가 떨어졌음.</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -2684,11 +2684,11 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>위치도 좋고 숙소 컨디션도 좋아요!</t>
+          <t>침대룸 1개 온돌 1개가  불편했다.침대룸 2개를  선택할수있는 옵션이  있었으면 한다.싱글배드로</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -2696,11 +2696,11 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>시설이 깨끗하고 화장실 비데가 아주 좋아요~~</t>
+          <t>하.. 2층 에어컨 곰팡이 냄새가 심해서 이틀간 역하고 머리아팠고 1층 화장실 바닥 군데군데 곰팡이며 정화조가 역류하는지 밤사이 변기에서 요란한  소리와 함께 냄새도 심했어요..</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -2708,11 +2708,11 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>좋아요 ~~~~~~~~~</t>
+          <t>휴식취하기에 좋은데 주말에는확실히 사람이 많습니다.특히스파의경우는 스파라기보단그냥 워터파크느낌이 강한데 사람이 많다 보니수질도 기대이하여서 아쉬웠네오. 주말피해서 가먄확실히 좋을듯 합니다</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -2720,11 +2720,11 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>무엇보다 뷰가 좋았고 바다가 가까워서 좋아요.주변에 맛집도 많습니다.</t>
+          <t>객실 깨끗하고 편히 쉬기 좋아요.화장실도 3개라 다수 인원이 가기좋아요.다만 취사가 불가하더라도 냉장고가 너무 작네요.기준 7인에 맞는 물을 넣을 공간도 없어요.음료를 사서 넣으니까 냉장고 작동조차 안됩니다.솔직히 기준7인에 맞는건 화장실밖에 없었어요.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -2732,11 +2732,11 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>잘쉬다갑니다~~~!!!</t>
+          <t>스파 해브나인 입장할 때 퇴장할 때 직원의 태도에 많이 실망했습니다.스파 내 이용시설에서 근무하시는 직원분들은 대체로 친절하고 설명도 자세했지만, 입장할 때 응대하던 직원의 응대가 굉장히 미흡해서 일관된 서비스가 아니었던게 아쉬웠습니다.전반적인 시설과 환경은 만족스러웠습니다.</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>매우 친절하시고 필요한 것들이 잘 갖춰져 있습니다. ^^</t>
+          <t>즐겁게 사용했습니다^^ 청소가 덜된부분도 있고 수도배관에서 냄새도 올라오고 그랬지만  큰  불편함은 없었습니다. 옆방 분들이 밤늦게까지 일행분들과 시끄럽게 해서 불편했습니다.</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -2756,11 +2756,11 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>휴식하기 좋았습니다 다시 또 오고 싶어요~^^ 전체적으로 다 좋았습니다~</t>
+          <t>깨끗하고 편안해서 쉬기 좋았어요~</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>깔끔하고 바다와 가까워서 놀기 좋았어요 역시 제주도는 👍</t>
+          <t>처음 가본 레스트리 리솜! S20이라 방 크기가 작을까 했지만 꽤나 큰 사이즈에 만족했으며 직원분들 너무 친절하시고 스파와 부대시설 이용하는 동선도 가까워 너무나 만족했던 여행이었습니다!</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>바다뷰가 좋아요직원친절하고 가성비는굿입니다</t>
+          <t>갈때마다 편하게쉬고와요^^</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -2792,11 +2792,11 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>경치도 좋고 방도 깨끗해서 좋았어요</t>
+          <t>산속에서 스파를 즐기기에 아주 좋습니다. 이동 동선이 다소 복잡하긴 하지만 좋아요</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>곽지해수욕장 앞에 있는 숙소라 편하고 좋아요.</t>
+          <t>작년에 포레스트 방문 후 레스트리는 처음이네요.잘 숙박했습니다^^</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -2816,11 +2816,11 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>바다에서 가깝고 나름 뷰도 있어서 잘쉬다가 왔습니다.</t>
+          <t>객실도깨끗하고 덕분에 잘쉬다왔습니다</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>앞에 바다가 바로 있어서 너무 좋았어요</t>
+          <t>룸은 깨끗하고 직원분들이 너무 친절 하세요</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>첫날부터 직원분들이 너무 친절하셨어요. 잘 놀다가 돌아 갑니다.</t>
+          <t>G50 레스트리 이용했는데내부도 고급스럽고 특히 욕실이 맘에 들었어요.</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>잘쉬다갔어요 만족합니다.</t>
+          <t>너무 힐링하고옴 ㅠㅠ</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>뷰가 장난아닙니다.해수욕장도 근접해서 너무좋습니다.음식점도 많고 또 방문할래요</t>
+          <t>아주 청결하고,깨끗하게 정돈되어 있음</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>곽지해변이랑 가깝고 시설 넓고 좋아요</t>
+          <t>아이와 가기 좋아요</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>3일동안 너무 편하게 머물렀습니다:)</t>
+          <t>쉬기에 좋은 곳이예요</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ㄹㅇ뷰맛집임 침대도 완전 푹신하고 일어나서 체크아웃하기 싫을정도로 아침뷰가 너무예쁨..</t>
+          <t>깔끔하고 넓고 아늑하고 뷰도 탁트이고 조용하게 즐길 수 있는 좋은 숙소였습니다</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>곽지해수욕장 바로앞에있어서 좋았어요</t>
+          <t>편안하고 조용하고 너무좋아여! 물도 따뜻하고 힐링하고왔습니다🩵😘🩵</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>직원분이 매우친절하고 뷰가 끝내주네요</t>
+          <t>너무 깨끗하고 공간도 좋고 행복한 시간이였습니다!</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>숙소가 깨끗하고 편의점ㆍ곽지해수욕장이 바로 앞이라 좋았어요^^잘 쉬고 왔습니다~</t>
+          <t>스파도 좋고 다 좋았습니다!</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -2948,11 +2948,11 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>위치며 뷰며 최고입니다 다시 방문할께요 쵝오 !!!</t>
+          <t>리조트 내 부대시설이 다양해서 너무 좋았습니다. 아이가 키즈카페도 좋아했습니다.</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>깨끗하고 아늑하고 친절하시고 좋앗습니다</t>
+          <t>깨끗하고 좋습니다.</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>청결하고 직원들도 친절하고 좋아요</t>
+          <t>분위기 정말 최고였어요</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>친절하시고 숙소도 아늑하고 뷰도 좋았어요</t>
+          <t>레스트리동 깨끗하고 편의시설 가까워서 좋았어요</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -2996,11 +2996,11 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>.....</t>
+          <t>객실정비잘되었고 좋았습니다.베개는 너무푹신해서불편했어요</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -3008,11 +3008,11 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>친절하고 좋았어요 편하게 쉬고 바다도 바로 앞이라 좋았습니다</t>
+          <t>작은방 보일러 고장. 거실 우풍이 너무 심함</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>너무 좋은 뷰에 위치도 좋고 깨끗햌ㅅ습니다!</t>
+          <t>부모님과 너무 잘 다녀왔습니다~ 스파패키지로 저렴하게 이용해서 좋았어요추천합니다</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>좋아오 잘 즐기다 갑니나</t>
+          <t>숙소도 청결하고 친절하고 좋았어요</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>방이 깔끔하고 뷰도 좋았습니다. 직원분들도 친절하시고요.잘 지내다 갑니다.</t>
+          <t>너무 잘 놀다왔습니다. 아이와 함께 여행가기 좋아요^^</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>좋았어요  sogood</t>
+          <t>3대 가족이 함께 갔을 때 할머니도 어린 아이들도 모두 만족하는 곳이었어요~</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -3068,11 +3068,11 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>전보다 많이 노후된 느낌이에요히터가 천장에서 바로 나오니 건조했어요</t>
+          <t>급하게갔는데 너무좋앗어요</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -3080,11 +3080,11 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>좋았습니다</t>
+          <t>겨울되면 또 갑니당 ㅎㅎ</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -3092,11 +3092,11 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>오션뷰 짱입니다😍</t>
+          <t>아이와 같이가서 잘놀고왔어요수영장에서도 재밌게 놀았어요</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>너무 만족스러워요!! 가격도 그렇고 방 컨디션도 그렇고^^</t>
+          <t>너무좋습니다^^ 역시 리솜입니다.</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>엄청 친절하세요 깔끔하고 좋습니다</t>
+          <t>너무좋습니다^^ 역시 리솜입니다.</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>앞에 곽지 해수욕장이 보여서 좋았습니다!</t>
+          <t>주차도 편하고 객실도 깨끗해요! 부대시설도 잘 갖춰있어 편하게 이용했습니다~</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>바다뷰 좋고 이뻐요</t>
+          <t>방 컨디션도 좋고 깨끗하네요!</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>방도 깨끗하고 사장님도 엄청 친절하세요</t>
+          <t>별자리 관측도 하고 숙소는 좋아요</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -3164,11 +3164,11 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2층이고오션뷰라좋았어요  나중에 다시가고싶어요</t>
+          <t>사우나 탕 물이 엄청깨끗해요다녀본곳중 제일 칭찬합니다</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>잘쉬다가갑니당</t>
+          <t>경치도 좋고 시설도너무좋아요</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>직원분들이 너무친절 하세요공항에서도 멀지도 않고 좋아요</t>
+          <t>경치도 좋고 시설도너무놓앗어요</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -3200,11 +3200,11 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>조용했어요</t>
+          <t>부대시설이 많아서 부모님과 아이와 가기좋아요~</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>잘놀다갑니다</t>
+          <t>여러번 방문해도 늘 갈때마다 좋다고 느끼는 곳입니다~</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>좀 춥습니다...</t>
+          <t>재밌게 잘 놀고 왔습니다</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>작년에 이용하고 재방문인데 여전히 좋았어요 ~!</t>
+          <t>빌라동 너무 조용하고 뷰가 멋져요</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>남친이랑 첫 제주도 여행이었는데 숙소도 넘 깨끗하고 좋았어요 ◡̈ 감사합니다 ◡̈</t>
+          <t>👍👍👍👍👍👍🫣</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -3260,11 +3260,11 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>아주굿. 해변도 바로</t>
+          <t>너무좋습니다 감사합니다</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -3272,11 +3272,11 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>합리적인 가격에 잠깐 머물기 좋아요</t>
+          <t>청결하고 좋았습니다.</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>가성비 좋아요~^^</t>
+          <t>비싼가격값합니다 ㅎㅎ</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>좋은 숙소였슴니다</t>
+          <t>비싼만큼 가격값해요</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -3308,11 +3308,11 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>약간 공간은 좁아보이나 불편함은 없네요. 침대가 편해서 아주 만족합니다.</t>
+          <t>가족들과 좋은 추억 나걌어요</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -3320,11 +3320,11 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>친절하시고 전반적으로 깨끗한편..~</t>
+          <t>전반적인 컨디션이나 청소 상태도 좋았습니다.</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -3332,11 +3332,11 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>숙소ㆍ렌트  괜찮았습니다</t>
+          <t>가족들과 함께 잘 지냈습니다</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -3344,11 +3344,11 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>친절하지만 시설대비 가격이 비싼편이다</t>
+          <t>스파이용할수있어서 좋았구 숙소도 깨끗해서 좋았어요!</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>넘좋았어요~~</t>
+          <t>직원들의 고객응대 수준이 다론 곳과 비교할 수 없을만큼 훌륭했습니다.</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>오 만족해요 싸고 잘잤어요 깨끗행ㅂ 직원들 모두 친절하시고.위치도 좋고 강추해요</t>
+          <t>제 맘 속 겨울에 꼭 와야하는 곳 선정 1위</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>주변 맛집 도보권에있고 청결해서 좋았어요</t>
+          <t>아이들과 함께하기 좋습니다.</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>바다뷰가 아주좋고 깔끔하고 편안한 숙박이었습니다.</t>
+          <t>아이들이 너무 좋아했습니다.숙소도 너무 깨끗하고,온천도 너무 좋았습니다.</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>너무 만족스럽네요 직원분들도 친절하고 위치도 대박이에요</t>
+          <t>한적하고 숲속에있어서 힐링하기 넘 좋았어요ㅠㅠ</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>깨끗하고 친절해서 좋았어요또 이용의사 있습니다.</t>
+          <t>깨끗하고 스파가 좋아요.</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>바다 코앞이라 즐길거리많고 잘쉬고 잘 잤습니다. 숙소 깨끗하고 좋았네요</t>
+          <t>깨끗하고 스파가 아이들 놀기에 좋아요.</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>급하게 잡았는데 너무친절해셔요~%</t>
+          <t>스파패키지로했는데 넘 만족합니당</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>뷰도 좋고 룸도 꽤 넓고 좋았어요.</t>
+          <t>설연휴 방문했는데 좋았습니다</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>잘쉬다갑니다~</t>
+          <t>아이와 시부모님과 함께 다녀왔는데 스파, 숙소, 조식 모두 만족스러웠습니다.</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -3476,11 +3476,11 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>너무너무좋았어요</t>
+          <t>직원친절도 최상.  숙소 정비나 시설이 깨끗하고 뒷산뷰도 조용하고 좋았습니다.</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>바다뷰로 바꿔주셔서 좋았어요~ 넷플릭스만 되면 더 좋을 것 같아요~</t>
+          <t>나이트 스파 이용하니 사람도 적고 별도 볼 수있어 좋았습니다</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -3500,11 +3500,11 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>잘머물다가요</t>
+          <t>숙소가 전반적으로 깨끗하고 스파가 인상적입니다.</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>제주도 첫날숙소로 잘다녀왔어요^^!</t>
+          <t>가족이랑 보내기 최고에요!</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -3524,11 +3524,11 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>숙소 깨끗하고 직원분들 친절하시고 뷰가 정말 좋아요!</t>
+          <t>깨끗하고 산책하기도 좋아요. 애들이랑 물놀이하기 좋구요. 재미있게 놀다왔습니다.</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>다음에 또 오고싶어요! 해수욕장도 바로 앞에 있고 숙소도 너무 좋아요</t>
+          <t>풍경도 멋지고 부대시설도 다양해서 너무 좋았어요^^</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>바다앞이넘 좋았어요 직원들도 넘 친절하시구여~</t>
+          <t>객실이 넓고(방2, 화2) 쾌적해서 숙박하기 굉장히 편했습니다. 재방문의사 완전 있음</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>친절하시고 아주좋아요</t>
+          <t>친절하고 깨끗했습니다시설도매우좋습니다</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>곽지해수욕장 바로 앞이어서 물놀이 하기 편하네요, 직원 모두 친절하고 객실 청결합니다.</t>
+          <t>스파시설이나 숙소 모두 좋아요!</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>위치도 좋고 뷰가 너무좋습니다강추합니다 땅봉</t>
+          <t>최고였어요 또 가고 싶네요</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>너무좋아요</t>
+          <t>잘 쉬고 왔습니다!!</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -3608,11 +3608,11 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>바로 앞에 해수욕장이 있어서 편리했어요</t>
+          <t>생각 이상으로 만족했습니다</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>제주도 첫날 숙소였는데 완전 좋았습니다❤️😍</t>
+          <t>너~~~무 좋아요 또 가고싶네요 ㅎㅎ</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>네 좋네요 이므라히모비치</t>
+          <t>직원들이 넘 친절합니다!굿굿굿굿!</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -3644,11 +3644,11 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>방에서 오래된 모텔 냄새가많이났어요 이돈이면 다른데 갈거같아요..</t>
+          <t>휴양으로는 매우 좋아요 산속이라 공기도 좋고 다만 스파는 사람이 많네요.</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -3656,11 +3656,11 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>바닷가와 가깝고 좋습니다</t>
+          <t>가족과 함께가기 너무 좋은곳이었어요^^</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>너무 만족하고 좋았습니다~~~</t>
+          <t>숙소나 스파 시설이 좋아 즐겁게 놀고 쉬다가 왔습니다.</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>직원분들 너무 친절하시고 바닷가와 접근성도 너무 좋습니다.</t>
+          <t>음식이 맛있고 직원들이 친절함</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>너무 대 만족 합니다^^</t>
+          <t>역시 유명한데는 그 이유가 있어요!!</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>너무만족하고 잘자고 갑니다</t>
+          <t>객실 업그레이드도 해주시고 너무 깔끔하고 다 좋았어요~</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -3716,11 +3716,11 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>청결하고 좋읍</t>
+          <t>아이랑 가족여행으로 다녀왔어요부대시설도 잘되어있고 방도 깔끔하고 좋았어요</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>생각보다 깔끔해서 좋앗습니덩</t>
+          <t>방이 예상보다 많이 작기는 했지만 친절도에 반했습니다🥰 재방문 의사 100프로 예요!!</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>주인분 너무 친절하시고 방도 완전 깨끗하고 좋아요</t>
+          <t>지난 여름 방문이후 눈 내리는 겨울에 방문한 리솜포레스트는 그야말로 힐링 그 자체입니다.</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>재방문 의사 많아요. 추천합니다</t>
+          <t>좋았습니다 재방문의사 있어요</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>친절 청결 쾌적 또 오겠습니다</t>
+          <t>가족들과 좋은시간 보내고  왔어요</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>친절하시고  깔끔해서 잘 쉬고 왔어요..</t>
+          <t>직원분들 다 너무 친절하고 주위에 식당이 없는게 아쉽지만 시설 나 식당들도 맛있어요 !</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -3788,11 +3788,11 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>생각보다 테라스가 좁아서 아쉬웟어요...</t>
+          <t>친절하고 깨끗하고 찜질방도 좋았어요</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -3800,11 +3800,11 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>후기를작성해주세요</t>
+          <t>숙소가 깨끗하고 좋았어요 ㅎㅎ</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>곽지해수욕장 앞에 있어서 좋았구요깨끗했어요</t>
+          <t>조용하고 전망이 좋아서 쉬면서 산책하기 좋아요.</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>친절합니다</t>
+          <t>전체적으로 만족했습니다~ 또 이용하겠습니다</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -3836,11 +3836,11 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>위치 정말 좋아요!</t>
+          <t>좋습니다 나쁘지않음온천도 기대이상 ㅎㅎ</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>바닷가가 인접해서 너무 좋았어여 깔끔하고!!</t>
+          <t>깨끗하고 풍경도 예쁘고 쉬다오기 좋은 숙소</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>만족합니다</t>
+          <t>힐링하는 숙소였슴다</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>곽지해변은 여기가 답입니다날에 따라 다르겠지만</t>
+          <t>아이와 스파하면서 즐거운 시간 보내고 왔네요 다시 방문할듯 합니다</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>바다 바로앞이라 경치도좋고 넓은객실에 좋은향기와 친절함이 더해져 좋은 여행이었습니다~^^</t>
+          <t>좋았습니다재방문 의사 잇습니다</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>깨끗하고 바다전망이 좋았습니다</t>
+          <t>너무 좋고 깨끗해요</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -3908,11 +3908,11 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>괜찮았어요</t>
+          <t>깨끗하고 아이랑 함께 이용할 부대시설이 많아요</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>사장님이 친절하네요</t>
+          <t>아이와 함께가기좋은숙소에요 맑은공기마시고 숙소안에서 다해결할수 있어 편히쉬다가 잘왔습니다</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>숙소 깨끗하고 좋았습니다!! 다음에 또 방문하고싶어요</t>
+          <t>너무 너무 좋아요~!</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>덕분에 즐거운 여행 했어요</t>
+          <t>서울에서 가깝고 힐링하기 좋아요룸 컨디션도 아주 굳</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>ㄴㄷㄱㄷㅅㄷㅅㄷㅅㅈ</t>
+          <t>좋았습니다‘ 부모님이 좋아하셨어요</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
@@ -3968,11 +3968,11 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>위치 굿! 방에서 보는 뷰는 베리 굿 사장님도 짱짱 친절</t>
+          <t>ㄱᆢㅅ~^~^^^^</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
@@ -3980,11 +3980,11 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>가족끼리가기에는 괜찮음 전망이 아주좋음 친절함</t>
+          <t>친절하시고 침구류 실내 깔끔해요 스파 너무좋고 온천여행오기 딱이네요 편하게 쉬다가요</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
@@ -3992,11 +3992,11 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>위치도 좋고 방도 깔끔하고 무엇보다 따뜻한 물이 너무 잘 나와서 좋았어요!</t>
+          <t>좋네요 ㅎ 재방문의사 있음</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
@@ -4004,11 +4004,11 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>잘쉬었다갑니다</t>
+          <t>생각보다 퀄리티나 서비스가 살짝 아쉬웠어요ㅜ</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>깨끗하고 좋았어요</t>
+          <t>날씨 좋은 날 포레스트도 이용 예정입니다</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>시설도 너무 깨끗하고 좋았어요</t>
+          <t>포레스트빌라 뷰가 정말정말 좋고 객실도 정말 깔끔해서 잘 쉬었습니다 스파도 넘 좋았습니다</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>쾌적하고 너무 좋았습니다</t>
+          <t>청결하고 친절하시고즐겁게 잘쉬고왔네요~또가고싶고 계절마다 다니고싶네요</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
@@ -4052,11 +4052,11 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>조아용조아용</t>
+          <t>스파즐길수 있는 스파 좋아요~</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>시설깨끗하고 뷰맛집이네요.재방문 의사있습니다.</t>
+          <t>부모님 모시고 다녀왔어요ㅎㅎ너무 좋으시다고 하셔서 다음에 또 올렵니다~^^</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>다좋아요 일회용슬리퍼로 바꾸면 더좋을듯요~~</t>
+          <t>여기..너무좋다.가을 겨울언제든 좋을듯</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>재밌게 편하게 잘 쉬다왔어요</t>
+          <t>다시 또 가고싶네요~~!!해브나인 스파도 좋은 경험이었어요ㅎㅎㅎㅎ</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
@@ -4100,11 +4100,11 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>곽지해수욕장 바로 앞이라서 전망좋고 해안도로 산책하기좋아요</t>
+          <t>여기는 역시 풀이 좋아요</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>침대커버이불이 깨끗햇어요담에 또 오고싶은곳입니다</t>
+          <t>리조트 중 가장 만족스러웠습니다</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
@@ -4124,11 +4124,11 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>오션뷰가 너무 이쁘고 시설도 깨끗했어요 근처 식당가도 많아서 좋아요</t>
+          <t>스파시간이 너무짧아서 아쉬워요뷰 좋은방 없어서 아쉬웠어요</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
@@ -4136,11 +4136,11 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>곽지해수욕장 앞이라 접근성은 좋아요~숙소 바로 앞에 편의점도있고 식당도 몇군데 있어요</t>
+          <t>시설 최고, 친절 최고 모든게 최고였습니다</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>잘 놀다갑니당</t>
+          <t>너무편하고 좋습미다</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>온돌방식이라 따뜻하고  짐풀고 개인용품쓰기에 넓고 좋았습니다.</t>
+          <t>연인과 함께 좋은추억 쌓고갑니다~</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>아주좋아요</t>
+          <t>숙소깨끗해서 놀랐어요스파도 넓어서 이곳저곳 너무좋았어요~</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>오션뷰가 최고입니다</t>
+          <t>전경도 예쁘고 겨울철 스파도 매력적이었어요.부대시설도 많아서 정말 멋진여행 하고 왔네요.</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>이틀연박으로 잘 쉬다왔어요</t>
+          <t>가보고싶은곳 와서정말좋았네요</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>깨끗하고 친절해요</t>
+          <t>마묵라운지엘피판검상</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>👍👍👍👍👍</t>
+          <t>처음 방문했는데 너무 좋았어요! 눈올 때 또 가고싶어요~</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>깔끔하고 조용한 분위기 좋은 호텔이었습니다</t>
+          <t>직원도 친철하고 부대시설도 전체적으로 만족합니다^^!</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>시설도 그렇고 직원들도 친절합니다</t>
+          <t>부모님과 함께 다녀왔습니다. 조용하니 휴양하기 좋았어요.</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>굿굿굿굿굿</t>
+          <t>자연속으로, 조용하게 그냥  쉼 그자체였다.</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>직원분들 너무친절했구요뷰도 좋았어요</t>
+          <t>산에서 하루 지내는기분이듭니다. 마침눈이와서 좋았구요. 다만 포레스트는 교통이 불편한점.</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>깔끔하고 좋아요</t>
+          <t>산에서 하루 지내는기분이듭니다. 마침눈이와서 좋았구요. 다만 포레스트는 교통이 불편한점.</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -4292,11 +4292,11 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>해수욕장이한눈에보이니 뷰가 최고예요시설도깔큼사니 좋네요</t>
+          <t>산에서 하루 지내는기분이듭니다. 마침눈이와서 좋았구요. 다만 포레스트는 교통이 불편한점.</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>더할 나위 없이 좋았습니다 ㅎㅎ</t>
+          <t>객실깔끔하고 너무 좋습니다~~~잘놀다왔어요 조식도 너무 맛있어요</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
@@ -4316,11 +4316,11 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>진짜 만족감 최고 오션뷰 최강입니다</t>
+          <t>숙소가 깔끔하고 관리 잘 된 느낌이예요.경치는 좋지만 주변이 조금 심심하기는 해요.</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>최고의 숙소였습니다 최고</t>
+          <t>객실 상태는 좋았으나 침대 기준 인원 4인입니다.</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
@@ -4340,11 +4340,11 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>좋네요  다시 가고픈 호텔</t>
+          <t>리솜 좋네요 좋아요!!!</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>완전 강추합니다.</t>
+          <t>너무 깨끗하고 좋았습니다! 직원들도 친절했어요</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
@@ -4364,11 +4364,11 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>기대가 너무 큰 탓이였을까요?</t>
+          <t>스파패키지에 저렴하게 예약하고 직원들도 친절하고 돈주고 갈만하네요~</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
@@ -4376,11 +4376,11 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>좋아요. 뷰가죽어요</t>
+          <t>좋아요. 또 가고싶어요</t>
         </is>
       </c>
       <c r="C329" t="inlineStr"/>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>방 깔끔하고 오션뷰 좋았어요다음에도 방문할게요</t>
+          <t>언제나 가도 좋은 포레스트 리솜입니다.다른 말이 필요 없는 것 같습니다.</t>
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
@@ -4400,11 +4400,11 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>바다가 바로앞에있어서 뷰가좋고 객실도 깨끗해요!</t>
+          <t>하루 쉬고 오기에 딱 좋네요산책코스도 공기도 숲냄새도 모든게 좋았습니다</t>
         </is>
       </c>
       <c r="C331" t="inlineStr"/>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>너무 깔끔했습니다</t>
+          <t>약간일찍와서 짐맡기고 스파즐겻는데 너무좋앗어요</t>
         </is>
       </c>
       <c r="C332" t="inlineStr"/>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>좋았습니다</t>
+          <t>숙수에 늦게 도착해서 수영은 못했지만 찜질방과 사우나만 이용했는데 너무 좋았어요ㅎㅎ</t>
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>객실 직원 비품 뷰 모든게 완벽했습니다</t>
+          <t>너무 좋았어요 공기도 좋고 어메니티 부대시설 등 다음에 재방문할 예정입니다 돈 값해요!</t>
         </is>
       </c>
       <c r="C334" t="inlineStr"/>
@@ -4448,11 +4448,11 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>제주 서쪽에 있을거면 가성비 좋은 호텔이예요.</t>
+          <t>저녁뷔페부터 룸 컨디션까지 너무 좋았습니다가을이라 풍경이 정말 아릅답습니다!</t>
         </is>
       </c>
       <c r="C335" t="inlineStr"/>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>청결 친절도 모두 최고였습니다 ! 뷰는 말해뭐합니까!!!!</t>
+          <t>프라이빗하고 정말 이뻐요</t>
         </is>
       </c>
       <c r="C336" t="inlineStr"/>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>컨디셔너 어디껀가요...???  하루종일 향이 너무 좋아요</t>
+          <t>즐거운 시간이었어요</t>
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2층이라서 조금 아쉬웠지만위치도좋고 뷰도 좋아서 만족</t>
+          <t>진짜 좋았어요. 부모님 모시고 와도 정말 좋을듯하네요</t>
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>깨끗하고 좋았습니다</t>
+          <t>시설과 전경 모두 만족합니다</t>
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>조아요오...</t>
+          <t>자연에 속에 있어서 산책하기 좋고 숙소도 아늑하고 편안했어요~ 욕실이 진짜 좋았어요!!</t>
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
@@ -4520,11 +4520,11 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>편하고 좋아요!</t>
+          <t>아주좋습니다 경치도좋구요 다마음에듭니다</t>
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>곽지해변 바로 앞이어서 너무 너무 힐링되네요~~</t>
+          <t>엄마와 이모모시고 다녀온 리솜~^^넘나 즐거웠습니다!</t>
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>기대한것보다 너무 깨끗하고 직원분들이 너무 친절하셨어용 또 올게유 ~~~!!</t>
+          <t>좋아서 다음에 또 이용하려구요</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>뷰 너무이쁘고 바다가 바로 앞이라서 넘 좋았어요^^</t>
+          <t>엄청나게 좋은 조경과 트래킹코스 방도 깨끗하여서 잘지내다왔습니다</t>
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>사진과 동일해요 좋았어요</t>
+          <t>조식이 가격대비 먹을건 없지만 가족과 즐겁게 쉬다갑니다</t>
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
@@ -4580,11 +4580,11 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>가족들 모두 대만족^^좋은 여행이었습니다~</t>
+          <t>경치가 예뻤고고 부대시설이 다양해서 가족들과 즐기기 좋았습니다.</t>
         </is>
       </c>
       <c r="C346" t="inlineStr"/>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>최고입니다~~</t>
+          <t>여기..대박~!!!!너무 너무 좋아요..가을 맛집입니다</t>
         </is>
       </c>
       <c r="C347" t="inlineStr"/>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>오션뷰가 좋고 해변가까워서 바다 수영하기에 최족의 호텔 같아요. 강추합니다.</t>
+          <t>애기 수영장이 워터풀과 미끄럼틀밖에없어서 아쉽.. 뷰는 인정</t>
         </is>
       </c>
       <c r="C348" t="inlineStr"/>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>카운터에 계신분들도 친절하고 방도 괜찮았어요!</t>
+          <t>친절한직원들덕분에 즐거운 여행했어요감사합니다</t>
         </is>
       </c>
       <c r="C349" t="inlineStr"/>
@@ -4628,11 +4628,11 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>물이 잘 안내려가는거 빼고는 나머지는 깨끗하고 좋았어요ㅎㅎ</t>
+          <t>좋앗던 기억이 큽니다 !!++</t>
         </is>
       </c>
       <c r="C350" t="inlineStr"/>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>프론트 직원분들 엄청 친절하세요! 시설도 엄청 좋고 뷰도 환상이예요!!!!😎😌</t>
+          <t>스파가 너무 좋았습니다^^</t>
         </is>
       </c>
       <c r="C351" t="inlineStr"/>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>친절하시고 쾌적하고 너무 즐거운여행이였어요!!뷰가 미쳤어요!</t>
+          <t>승강기가 오래걸리는거 제외하곤 만족스러웠습니다 ^^</t>
         </is>
       </c>
       <c r="C352" t="inlineStr"/>
@@ -4664,11 +4664,11 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>잘쉬다갑니다 뷰가 너무 좋아용</t>
+          <t>친구들과 가게 된 숙소였는데 깨끗하고 친절한 대응이 너무 좋았습니다.</t>
         </is>
       </c>
       <c r="C353" t="inlineStr"/>
@@ -4676,11 +4676,11 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>힐링 넘 잘하고갑니다 강추^^</t>
+          <t>직원분들께서너무친절합니다매우기분좋은 여행이었습니다</t>
         </is>
       </c>
       <c r="C354" t="inlineStr"/>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>무난무난 했습니다 곽지해수욕장에서 놀기에 좋고 편의시설도 주변에 나쁘지 않았어요~</t>
+          <t>가족들이랑 정말 좋은 시간 보냈어요! 다음에 또 오고싶을만큼 풍경이 예쁜 곳이었습니다.</t>
         </is>
       </c>
       <c r="C355" t="inlineStr"/>
@@ -4700,11 +4700,11 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>바다뷰도 좋고 방 화장실 넘 깨끗함</t>
+          <t>인피니티풀이 너무 더러워서 놀랐어요</t>
         </is>
       </c>
       <c r="C356" t="inlineStr"/>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>뷰도 좋고 하루 잘 지내고 왔어요 ㅎㅎ</t>
+          <t>가족여행갔었는데 아주좋았습니다</t>
         </is>
       </c>
       <c r="C357" t="inlineStr"/>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>기대이상으로 좋았고 또 이용할 생각이에요~</t>
+          <t>물이정말 좋았습니다. 놀러가기에 정말 좋은 장소였어요</t>
         </is>
       </c>
       <c r="C358" t="inlineStr"/>
@@ -4736,11 +4736,11 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>위치도좋고 직원분들도 친절하셨지만 침대는 좋지못했어요....</t>
+          <t>전체적으로 만족스럽습니다</t>
         </is>
       </c>
       <c r="C359" t="inlineStr"/>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>좋았어요~다음에 또 이용할께요^^</t>
+          <t>가족숙소로 추천합니다. 해브나인은 어르신들과 오기 좋은곳 같아요.</t>
         </is>
       </c>
       <c r="C360" t="inlineStr"/>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>다음에 또 묵을거에요근처에 맛집들도 많고 숙소도 너무 깔끔하고 최고에요</t>
+          <t>산속휴향느낌이라 아주 만족했어요부모님도 좋아하셨구요</t>
         </is>
       </c>
       <c r="C361" t="inlineStr"/>
@@ -4772,11 +4772,11 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>깨끗하고 직원분들이 친절합니다거실에 스타일러도 있다니요</t>
+          <t>최고에요 나이트스파도 좋고 시크릿스파도 최고입니다</t>
         </is>
       </c>
       <c r="C362" t="inlineStr"/>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>뷰맛집 찐이에요 ㅠㅠ앞으로도 자주 애용할것같아요 주변에 맛집도 많고 너무 행복했습니다~</t>
+          <t>진짜 스파가 최고였습니다. 주말방문시 나이트 스파 필수!!!!</t>
         </is>
       </c>
       <c r="C363" t="inlineStr"/>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>좋았습니다~</t>
+          <t>가을에 부모님 모시고 가기 좋아요~</t>
         </is>
       </c>
       <c r="C364" t="inlineStr"/>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>바다가 바로앞에 보이는곳이라 그런지 좋았습니다</t>
+          <t>스파 시설이 잘 되어 있어요수영장 내에 매점? 있어서 편리해요</t>
         </is>
       </c>
       <c r="C365" t="inlineStr"/>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>넘 좋았어요ㅎㅎㅎㅎ</t>
+          <t>힐링하기 넘 좋아요</t>
         </is>
       </c>
       <c r="C366" t="inlineStr"/>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>좋습니다. 추천합니다.</t>
+          <t>부모님 아이와 방문했는데 너무 좋았어요!객실 청결이며 부대시설 모두 훌륭해오</t>
         </is>
       </c>
       <c r="C367" t="inlineStr"/>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>다좋았어요.바다는 손톱만큼 보임 주의.</t>
+          <t>숲속 경치가 좋아 힐링하기 좋고 아이와 즐길거리도 많습니다.</t>
         </is>
       </c>
       <c r="C368" t="inlineStr"/>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>좋았습니다</t>
+          <t>경치가 좋고 스파가 좋았습니다</t>
         </is>
       </c>
       <c r="C369" t="inlineStr"/>
@@ -4868,11 +4868,11 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>해수욕장 근처에요</t>
+          <t>가족들과 함께 가기엔 최고여유가을마다 생각나는 제천리솜</t>
         </is>
       </c>
       <c r="C370" t="inlineStr"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>뷰가 정말 예술입니다 또 방문 예정이에요</t>
+          <t>리솜포레스트 경치도 스파도 모두 만족이에요♡</t>
         </is>
       </c>
       <c r="C371" t="inlineStr"/>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>바다앞이라 뷰가 좋습니다.</t>
+          <t>경관도 좋고 스파 시설도 좋았습니다</t>
         </is>
       </c>
       <c r="C372" t="inlineStr"/>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>가성비 좋아요</t>
+          <t>만족스러운 리조트가족모두 힐링하고 갑니다</t>
         </is>
       </c>
       <c r="C373" t="inlineStr"/>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>곽지해수욕장 바로 앞이라 바다가 잘보이고, 산책하기도 좋았어요 ㅎㅎ 잘 머물렀습니다 :)</t>
+          <t>공기 너무 좋고 키즈프렌들리합니다~ 시설도 좋아용</t>
         </is>
       </c>
       <c r="C374" t="inlineStr"/>
@@ -4928,11 +4928,11 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>괜찮아요.</t>
+          <t>너무 좋았어요 자연속에서 힐링하는 느낌</t>
         </is>
       </c>
       <c r="C375" t="inlineStr"/>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>깔끔하고 좋았어요</t>
+          <t>편하게 잘 쉬다갑니다</t>
         </is>
       </c>
       <c r="C376" t="inlineStr"/>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>첫날 첫숙소 너무 친절하셔서 스타트가 좋았어요^^</t>
+          <t>몬도키친 대박입니다</t>
         </is>
       </c>
       <c r="C377" t="inlineStr"/>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>너무아름다운방이었어요침대넓고훌륭해요</t>
+          <t>항상 매우 만족하는 숙소입니다</t>
         </is>
       </c>
       <c r="C378" t="inlineStr"/>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>좋은추억감가핮다</t>
+          <t>매년 한번씩은 가는것 같아요 갈때마다 힐링하고 옵니다</t>
         </is>
       </c>
       <c r="C379" t="inlineStr"/>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>너무 잘다녀와ㅛ슺니다~</t>
+          <t>가족여행으로 좋네요</t>
         </is>
       </c>
       <c r="C380" t="inlineStr"/>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>좋아요~~~</t>
+          <t>숙소는 좋았으나 직원분들의 서비스는 별로였음</t>
         </is>
       </c>
       <c r="C381" t="inlineStr"/>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>만족합니다!</t>
+          <t>정말 역대급으로 좋았어요 뷰도 좋고 가족들과 또 가보려고요</t>
         </is>
       </c>
       <c r="C382" t="inlineStr"/>
@@ -5028,21 +5028,1437 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>직원분들친절하시고 뷰도넘좋았어요~재방문할께요^^~</t>
+          <t>가족끼리 가기 좋아요</t>
         </is>
       </c>
       <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr"/>
     </row>
     <row r="384">
-      <c r="A384" t="inlineStr"/>
-      <c r="B384" t="inlineStr"/>
-      <c r="C384" t="n">
-        <v>4.662303664921466</v>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>좋(59), 좋았어요(44), 있어(43), 뷰(42), 바로(39), 좋았습니(35), 깨끗(34), 좋아요(30), 직원분(29), 편(27), 앞(27), 깔끔(27), 친절하시(25), 객실(24), 있(24)</t>
+      <c r="A384" t="n">
+        <v>5</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>자연과 함께 할 수 있어 힐링되었습니다</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>5</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>자연과 함께 할 수 있어 힐링되었습니다</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr"/>
+      <c r="D385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>5</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>청결도 시설 모두 만족합니다</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr"/>
+      <c r="D386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>5</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>깔끔함 그 잡채 !</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr"/>
+      <c r="D387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>5</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>시설도 깨끗하고 스파도 너무좋아요</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr"/>
+      <c r="D388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>5</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>수영장이 좋고 아이와 즐겁게 놀았습니다.</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>5</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>아이와 수영하기 좋고, 부대시설의 음식들이 평균 이상입니다.</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>5</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>리뉴얼한 찜질방 좋아요 공기좋고 물좋고 3대가 잘 쉬고 왔습니다!!</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>5</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>매우만족스럽습니다 다음에도 올거에요</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>5</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>조식뷔페 뷰가 참 좋았어요!!!</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>5</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>수영장과 스파시설이 국내최고입니다</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr"/>
+      <c r="D394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>4</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>숙소도 깨끗하고 직원들도 친절하고 좋음단. 카트 이동과 계단 이동은 불편함</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>5</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>역시 숙소 좋네요~~</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr"/>
+      <c r="D396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>5</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>너무 만족하고 힐링하고 갑니다</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>5</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>뷰도 좋고 넓어서 힐링하고 갑니다!!</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr"/>
+      <c r="D398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>5</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>조용히 쉬다오기 좋아요 ㅎ</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr"/>
+      <c r="D399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>5</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>주차가 협소하여 불편했지만 경치와 룸컨디션좋아서 너무 좋았어요 다음에 또가고싶네요</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr"/>
+      <c r="D400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>5</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>부모님과 함께 간 여행인데 부대시설, 산책길이 잘 되어 있어서 좋아요! 조식도 맛있어요!</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr"/>
+      <c r="D401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>5</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>가족과 가기 좋아요~ 레스트리는 어린아이랑 있으몀 강추스파는 꼭 하세요</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr"/>
+      <c r="D402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>4</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>방 3개 화장실 3개로 인원수 많은 가족여행으로 만족스러운 숙박이었습니다.</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr"/>
+      <c r="D403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>5</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>항상 가고있어요~10월에 또 가야쥬</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr"/>
+      <c r="D404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>5</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>항상 자주 가는곳..너무 좋아요~가을에 또 갈거예요</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr"/>
+      <c r="D405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>5</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>가족여행으로 다녀왔습니다. 깔끔하고 행복한 시간 보냈습니다.</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr"/>
+      <c r="D406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>5</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>5인 가족 편하게 묵었어요. 침구도 깨끗하고요. 날 추워지면 또 오고 싶어요</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr"/>
+      <c r="D407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>5</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>가족여행스파 즐기고 숙소에서 잘 자고 갑니다숙소 방음 잘되네요!!!!!!!</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr"/>
+      <c r="D408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>3</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>스파랑 글램핑하고싶었는데갑자기날씨가안좋아져서못했넹노ㅠ아쉽</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr"/>
+      <c r="D409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>5</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>3번째여행깨끗하고  친절해요다만 수영외엔 놀거리가 부족해요</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr"/>
+      <c r="D410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>5</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>여행에 있어 중요한 쉼과 먹거리와 놀거리가완벽하게 갖춰져 있어요.</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr"/>
+      <c r="D411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>5</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>탁 트인 시야로 숲이 보이고~ 시설도 좋고~ 가족끼리 잘 쉬다가 왔습니다!</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr"/>
+      <c r="D412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>4</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>가족휴가중 1박2일 즐겁게 잘 지내다왔습니다</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>4</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>너무좋았습니다! 가족들이랑 여행오기 좋아요</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>5</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>어른 아이 모두 즐길수있는곳</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>5</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>숙소아주 청결합니다 직원분들 넘친절하시고 담에 또가고싶어요</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr"/>
+      <c r="D416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>5</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>비 오는 날이었는데도 너무 좋았어요 잘 쉬다 갑니다</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr"/>
+      <c r="D417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>5</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>좋은곳애서 잘묵고왔습니다</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr"/>
+      <c r="D418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>4</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>가족들과 잘 쉬다가 갑니다!</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr"/>
+      <c r="D419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>5</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>정말 최고입니다 또  가고싶어요</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr"/>
+      <c r="D420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>4</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>레스트리 숙소 깨끗하고 편안했어요침구가 좋았고 직원들도 친절하게 응대해 주었어요</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr"/>
+      <c r="D421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>5</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>리조트 컨디션부터 해브나인 스파까지 너무 좋았습니다. 국내 휴식 장소로 정말 좋아요</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr"/>
+      <c r="D422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>5</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>좋아요좋ㅇ아 완전 좋아요</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr"/>
+      <c r="D423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>5</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>좋습니다. 산속에 있어 접근성은 조금 떨어지지만 다른 것들은 다 좋았습니다</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr"/>
+      <c r="D424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>5</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>공기도 좋고 힐링하기 좋습니다</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr"/>
+      <c r="D425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>5</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>산속에서 하는 스파가 너무좋도시설도 깨끗하고 좋았어요</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr"/>
+      <c r="D426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>4</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>재밌었습니다날도좋고 룸서비스는 시간이좀 걸리나 친절하십니다</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr"/>
+      <c r="D427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>5</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>믿고가는 리솜! 즐거운 시간보냈습니다.</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr"/>
+      <c r="D428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>5</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>부모님 여행보내드렸는데 너무 잘다녀오셨다고 해요!!</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr"/>
+      <c r="D429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>4</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>산속 풍경이 좋고 산책로가 예뻐요 맑은 공기는 덤이에여</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr"/>
+      <c r="D430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>5</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>시설도 깨끗하고 자연에 둘러쌓여 있어서 힐링하기 넘  좋아요!!</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr"/>
+      <c r="D431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>5</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>숙소도 깨끗하고 리조트안에서 다할수있어서 편하고 좋았어요</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr"/>
+      <c r="D432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>5</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>최고입니다. 잘쉬구갑니다</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr"/>
+      <c r="D433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>5</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>말이 필요없는 힐링휴양지♡</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr"/>
+      <c r="D434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>5</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>공기좋고 나무냄새와 새소리가 참 좋았습니다</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr"/>
+      <c r="D435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>5</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>체크인시 친절하게 설명해주시고 리조트내에 시설들이 잘 되어있어 알차게 쉴 수 있었어요</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr"/>
+      <c r="D436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>4</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>한적하고 조용하나 교통접근성은 멀고가성비 될만한 사항은 늘려야할거 같음</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr"/>
+      <c r="D437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>4</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>산속 안에 있어서 자연을 느낄수 있어서 좋았어요!</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr"/>
+      <c r="D438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>5</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>가족끼리 편하게 다녀왔어요</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr"/>
+      <c r="D439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>5</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>리솜은 항상 대만족입니다. 가족 여행 추천이요!!!</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr"/>
+      <c r="D440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>5</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>리솜은 항상 대만족입니다. 가족 여행 추천이요^^</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr"/>
+      <c r="D441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>5</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>리솜은 항상 대만족입니다. 가족 여행 추천이요</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr"/>
+      <c r="D442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>5</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>부모님 모시고 오기 좋은 곳입니다ㅎㅎ</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr"/>
+      <c r="D443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>5</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>깔끔하고 좋음 기대치만큼</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr"/>
+      <c r="D444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>5</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>행복한 휴일 보냈습니다.</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr"/>
+      <c r="D445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>5</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>4시에 체크인했더니 1층뿐이 없다고해서 아쉬웠는데 방에가니 뷰 아주 맘에들었습니다.</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr"/>
+      <c r="D446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>5</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>외관부터 너무 아름다웠고 시설도 너무 좋았습니다</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr"/>
+      <c r="D447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>5</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>가을에 또 가고 싶어요👍</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr"/>
+      <c r="D448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>5</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>최고의 숙소입니디…^^</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr"/>
+      <c r="D449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>5</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>숙소가 깨끗하고 산책하기 너무 좋았습니다!</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr"/>
+      <c r="D450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>4</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>잘쉬었다갑니다요!!</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr"/>
+      <c r="D451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>5</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>첫방문이었는데 너무 좋았어요</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr"/>
+      <c r="D452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>1</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>최악입니다 직원들 불친절하고 시설도 사진만 그럴듯하지 막상가보면 별볼일없습니다</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr"/>
+      <c r="D453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>5</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>너무너무 예쁘게 잘해놨어요 또 가고싶네요ㅎㅎㅎ</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr"/>
+      <c r="D454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>5</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>좋았습니다ㅎ강추합니다</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr"/>
+      <c r="D455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>5</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>처음부터 마지막까지 너무 좋았어요부모님 모시고 가기 정말 좋습니다</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr"/>
+      <c r="D456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>1</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>체크인시 방 배정오류 등으로 문자다수발생,직원 서비스 매우 불량</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr"/>
+      <c r="D457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>5</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>역시나 넘 좋더라구용 또 가고파요</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr"/>
+      <c r="D458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>4</v>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>산책길에 수선화가 예쁘게 피었어요</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr"/>
+      <c r="D459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>3</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>주변지인들이 추천해서 다녀왔어요아이들과 시간보내기 좋은 장소같아요</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr"/>
+      <c r="D460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>5</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>깨끗하게 잘 관리된 거같아요</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr"/>
+      <c r="D461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>5</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>스파가 너무 좋고 숙박시설조 깔끔해서 편안하기 놀다 왔습니다</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr"/>
+      <c r="D462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>5</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>친절하시고 조식도 맛있고 힐링입니다.</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr"/>
+      <c r="D463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>5</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>너무 잘 쉬다가 갑니다 가족여행 숙소로 최고에요</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr"/>
+      <c r="D464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>5</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>굿굿베리굿!</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr"/>
+      <c r="D465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>5</v>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>단골입니다 시간 여유 생길때마다 가려고 합니다!</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr"/>
+      <c r="D466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>5</v>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>단골입니다 시간 여유 생길때마다 갈 생각입니다</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr"/>
+      <c r="D467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>4</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>생각한거보다 아기들이 많아서 좀 그랫지만 그래도 너무 좋았어용!</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr"/>
+      <c r="D468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>5</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>가격이 쎈거 빼고는 다 만족했습니다 좋네요</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr"/>
+      <c r="D469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>4</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>편한하게 쉬었다가 갑니다.</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr"/>
+      <c r="D470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>5</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>편한하게 쉬었다가 갑니다.</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr"/>
+      <c r="D471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>5</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>아기와 다녀왔는데 너무 좋았습니다</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr"/>
+      <c r="D472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>5</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>가족여행으로 왔는데 아침에 둘레길도 돌고 힐링됬어요 푹 쉬다 갑니다^^</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr"/>
+      <c r="D473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>5</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>가족 여행 너무 좋았어요 직원들도 친절하고 푹 쉬다 갑니다^^</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr"/>
+      <c r="D474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>5</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>제천이 전북에서 멀긴하지만 시설 좋아요아이들과 함께가기에 너무 좋은 숙소입니다</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr"/>
+      <c r="D475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>4</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>나름 좋아하는 부분 잇음</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr"/>
+      <c r="D476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>5</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>깨끗하고 넓고 스파 좋았습니다</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr"/>
+      <c r="D477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>5</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>즐겁게 힐링했어요ㅎㅎ</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr"/>
+      <c r="D478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>5</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>예상대로 전체적으로 좋았어요</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr"/>
+      <c r="D479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>5</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>너므좋았습니다</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr"/>
+      <c r="D480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>5</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>빌라동에 묵었는데 조용하니 정말 좋았습니다</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr"/>
+      <c r="D481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>5</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>감사합니다</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr"/>
+      <c r="D482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>5</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>체크인 할 때 시간이 엄청 오래 걸려요~</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr"/>
+      <c r="D483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>5</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>평일에도 사람 많았지만 부모님들. 아이들 모두 잘 쉬다갑니다^^</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr"/>
+      <c r="D484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>5</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>숙소는 전체적으로 괜찮은데 서비스나 직원들 친절도에서는 별로네요</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr"/>
+      <c r="D485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>5</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>외관이 멋진 건물이고룸컨디션도 훌륭!!다음에 또 오고싶은 곳^^</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr"/>
+      <c r="D486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>5</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>풍경도 좋고 전반적으로 관리가 잘되어있어 좋았어요.^^</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr"/>
+      <c r="D487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>5</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>매우만족합니다</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr"/>
+      <c r="D488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>4</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>지인과 함께한 리솜 넘 행복한 하룻밤이였습니다</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr"/>
+      <c r="D489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>3</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>.....</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr"/>
+      <c r="D490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>5</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>숙소 좋았습니다</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr"/>
+      <c r="D491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>5</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>역시 명불허전입니다.</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr"/>
+      <c r="D492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>4</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>휴식이 목적이라면 충분히 추천</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr"/>
+      <c r="D493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>5</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>평일이라 사람도 많이 없고 좋았습니다.모두 친절하셔서 잘 다녀왔어요</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr"/>
+      <c r="D494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>5</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>친구들과 여러명이서 놀기좋습니다! 방도 따뜻해요! 직원분들이 친절하세요!</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr"/>
+      <c r="D495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>5</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>다음에 방문하겠습니다</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr"/>
+      <c r="D496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>4</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>서비스는 좋아요!!!시설이 노후하가 도어서 일까요?추웠어요!!!!</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr"/>
+      <c r="D497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>5</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>최고의 숙소</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr"/>
+      <c r="D498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>5</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>너무 좋았어요ㅡ비싸서 후덜덜했지만 하나도 아깝지 않았어요</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr"/>
+      <c r="D499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>5</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>룸도청결하고 산속이라 조용해서좋아요 스파정말힐링됩니다</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr"/>
+      <c r="D500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>4</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>국내에서 온천수영장 이용시 편한곳은 여기뿐인거같네요 좋은추억만들었습니다</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr"/>
+      <c r="D501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr"/>
+      <c r="B502" t="inlineStr"/>
+      <c r="C502" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>좋(64), 스파(58), 깨끗(52), 좋았어요(48), 좋았습니(42), 숙소(39), 있어(32), 레스트리(31), 좋은(30), 좋아요(29), 많(29), 만(28), 있(27), 친절(27), 스파도(26)</t>
         </is>
       </c>
     </row>
